--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B6" t="n">
-        <v>98976</v>
+        <v>75006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,21 +1085,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R6" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002212</v>
+        <v>126002195</v>
       </c>
       <c r="B7" t="n">
-        <v>75006</v>
+        <v>98978</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630082</v>
+        <v>630152</v>
       </c>
       <c r="R7" t="n">
-        <v>6665660</v>
+        <v>6665487</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1271,7 +1271,7 @@
         <v>126002235</v>
       </c>
       <c r="B8" t="n">
-        <v>97003</v>
+        <v>97005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>58506</v>
+        <v>56597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,39 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R9" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1448,18 +1443,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>56597</v>
+        <v>58506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,34 +1478,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R10" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1551,12 +1545,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002222</v>
+        <v>126002189</v>
       </c>
       <c r="B11" t="n">
-        <v>95781</v>
+        <v>103765</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630048</v>
+        <v>630176</v>
       </c>
       <c r="R11" t="n">
-        <v>6665785</v>
+        <v>6665491</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,11 +1650,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002185</v>
+        <v>126002222</v>
       </c>
       <c r="B12" t="n">
-        <v>91193</v>
+        <v>95783</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,34 +1688,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630050</v>
+        <v>630048</v>
       </c>
       <c r="R12" t="n">
-        <v>6665784</v>
+        <v>6665785</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1755,12 +1754,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1779,10 +1784,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002189</v>
+        <v>126002220</v>
       </c>
       <c r="B13" t="n">
-        <v>103763</v>
+        <v>75006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,38 +1795,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630176</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665491</v>
+        <v>6665505</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1862,7 +1863,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B15" t="n">
-        <v>75006</v>
+        <v>91193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1989,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R15" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2172,42 +2172,39 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B17" t="n">
-        <v>57811</v>
+        <v>58506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2215,10 +2212,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R17" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2253,12 +2250,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2277,10 +2280,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002227</v>
+        <v>126002191</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>57811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,34 +2291,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630081</v>
+        <v>630106</v>
       </c>
       <c r="R18" t="n">
-        <v>6665659</v>
+        <v>6665554</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2374,50 +2385,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B19" t="n">
-        <v>58506</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002219</v>
+        <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>75006</v>
+        <v>96587</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630108</v>
+        <v>630009</v>
       </c>
       <c r="R20" t="n">
-        <v>6665515</v>
+        <v>6665706</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2579,45 +2579,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002178</v>
+        <v>126024178</v>
       </c>
       <c r="B21" t="n">
-        <v>96585</v>
+        <v>75006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630009</v>
+        <v>630163</v>
       </c>
       <c r="R21" t="n">
-        <v>6665706</v>
+        <v>6665743</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2639,17 +2642,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,6 +2666,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002196</v>
+        <v>126002219</v>
       </c>
       <c r="B22" t="n">
-        <v>98976</v>
+        <v>75006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2687,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2711,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630120</v>
+        <v>630108</v>
       </c>
       <c r="R22" t="n">
-        <v>6665550</v>
+        <v>6665515</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2773,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024178</v>
+        <v>126024175</v>
       </c>
       <c r="B23" t="n">
         <v>75006</v>
@@ -2802,19 +2811,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630163</v>
+        <v>630159</v>
       </c>
       <c r="R23" t="n">
-        <v>6665743</v>
+        <v>6665738</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2849,18 +2855,12 @@
           <t>2025-06-14</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75006</v>
+        <v>98978</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,7 +2979,7 @@
         <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>103763</v>
+        <v>103765</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>95781</v>
+        <v>95783</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3175,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002184</v>
+        <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>91193</v>
+        <v>95687</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630041</v>
+        <v>630171</v>
       </c>
       <c r="R27" t="n">
-        <v>6665802</v>
+        <v>6665468</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002193</v>
+        <v>126002184</v>
       </c>
       <c r="B28" t="n">
-        <v>95685</v>
+        <v>91193</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630171</v>
+        <v>630041</v>
       </c>
       <c r="R28" t="n">
-        <v>6665468</v>
+        <v>6665802</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B29" t="n">
-        <v>96585</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R29" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,32 +3466,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024176</v>
+        <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>75006</v>
+        <v>96587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630066</v>
+        <v>630049</v>
       </c>
       <c r="R30" t="n">
-        <v>6665750</v>
+        <v>6665789</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3563,32 +3563,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126024166</v>
+        <v>126024176</v>
       </c>
       <c r="B31" t="n">
-        <v>91228</v>
+        <v>75006</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630159</v>
+        <v>630066</v>
       </c>
       <c r="R31" t="n">
-        <v>6665490</v>
+        <v>6665750</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>95685</v>
+        <v>75006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R32" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R33" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,50 +3854,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126002172</v>
+        <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>58506</v>
+        <v>96587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630047</v>
+        <v>630074</v>
       </c>
       <c r="R34" t="n">
-        <v>6665787</v>
+        <v>6665750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,17 +3919,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3943,7 +3933,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024169</v>
+        <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>57648</v>
+        <v>96587</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3973,38 +3962,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630101</v>
+        <v>630065</v>
       </c>
       <c r="R35" t="n">
-        <v>6665757</v>
+        <v>6665730</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4037,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4068,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024162</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>96585</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,34 +4059,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630074</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665750</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4139,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,45 +4154,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024163</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>96585</v>
+        <v>58506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630065</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665730</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4230,12 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002175</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>58506</v>
+        <v>95687</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,39 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208250</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630182</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665478</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4332,17 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4351,7 +4341,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4373,7 +4362,7 @@
         <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>97437</v>
+        <v>97439</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4467,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>95685</v>
+        <v>58506</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,34 +4467,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R40" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4532,12 +4526,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4546,6 +4545,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B42" t="n">
-        <v>96585</v>
+        <v>4778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R42" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002197</v>
+        <v>126024164</v>
       </c>
       <c r="B43" t="n">
-        <v>98976</v>
+        <v>96587</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630142</v>
+        <v>630182</v>
       </c>
       <c r="R43" t="n">
-        <v>6665504</v>
+        <v>6665719</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002221</v>
+        <v>126002181</v>
       </c>
       <c r="B44" t="n">
-        <v>75006</v>
+        <v>96587</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630152</v>
+        <v>630057</v>
       </c>
       <c r="R44" t="n">
-        <v>6665501</v>
+        <v>6665764</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4956,10 +4956,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024182</v>
+        <v>126002221</v>
       </c>
       <c r="B45" t="n">
-        <v>4778</v>
+        <v>75006</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,21 +4967,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630146</v>
+        <v>630152</v>
       </c>
       <c r="R45" t="n">
-        <v>6665537</v>
+        <v>6665501</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126024164</v>
+        <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>96585</v>
+        <v>98978</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630182</v>
+        <v>630142</v>
       </c>
       <c r="R46" t="n">
-        <v>6665719</v>
+        <v>6665504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126002194</v>
+        <v>126024180</v>
       </c>
       <c r="B47" t="n">
-        <v>95685</v>
+        <v>75006</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630166</v>
+        <v>630152</v>
       </c>
       <c r="R47" t="n">
-        <v>6665496</v>
+        <v>6665543</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002192</v>
+        <v>126024179</v>
       </c>
       <c r="B48" t="n">
-        <v>95685</v>
+        <v>75006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630144</v>
+        <v>630188</v>
       </c>
       <c r="R48" t="n">
-        <v>6665747</v>
+        <v>6665726</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024180</v>
+        <v>126002192</v>
       </c>
       <c r="B49" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630152</v>
+        <v>630144</v>
       </c>
       <c r="R49" t="n">
-        <v>6665543</v>
+        <v>6665747</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126024179</v>
+        <v>126002194</v>
       </c>
       <c r="B50" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630188</v>
+        <v>630166</v>
       </c>
       <c r="R50" t="n">
-        <v>6665726</v>
+        <v>6665496</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R32" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B33" t="n">
-        <v>95687</v>
+        <v>75006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R33" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024162</v>
+        <v>126024169</v>
       </c>
       <c r="B34" t="n">
-        <v>96587</v>
+        <v>57648</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,34 +3865,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630074</v>
+        <v>630101</v>
       </c>
       <c r="R34" t="n">
-        <v>6665750</v>
+        <v>6665757</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3925,6 +3929,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,45 +3960,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024163</v>
+        <v>126002172</v>
       </c>
       <c r="B35" t="n">
-        <v>96587</v>
+        <v>58506</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630065</v>
+        <v>630047</v>
       </c>
       <c r="R35" t="n">
-        <v>6665730</v>
+        <v>6665787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4016,12 +4030,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4030,6 +4049,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4048,10 +4068,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126024162</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>96587</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,38 +4079,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630074</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665750</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,11 +4139,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4154,50 +4165,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024163</v>
       </c>
       <c r="B37" t="n">
-        <v>58506</v>
+        <v>96587</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630065</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665730</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4230,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024182</v>
+        <v>126024164</v>
       </c>
       <c r="B42" t="n">
-        <v>4778</v>
+        <v>96587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630146</v>
+        <v>630182</v>
       </c>
       <c r="R42" t="n">
-        <v>6665537</v>
+        <v>6665719</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4762,7 +4762,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126024164</v>
+        <v>126002181</v>
       </c>
       <c r="B43" t="n">
         <v>96587</v>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630182</v>
+        <v>630057</v>
       </c>
       <c r="R43" t="n">
-        <v>6665719</v>
+        <v>6665764</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002181</v>
+        <v>126002197</v>
       </c>
       <c r="B44" t="n">
-        <v>96587</v>
+        <v>98978</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630057</v>
+        <v>630142</v>
       </c>
       <c r="R44" t="n">
-        <v>6665764</v>
+        <v>6665504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002197</v>
+        <v>126024182</v>
       </c>
       <c r="B46" t="n">
-        <v>98978</v>
+        <v>4778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222302</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630142</v>
+        <v>630146</v>
       </c>
       <c r="R46" t="n">
-        <v>6665504</v>
+        <v>6665537</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126024180</v>
+        <v>126002192</v>
       </c>
       <c r="B47" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630152</v>
+        <v>630144</v>
       </c>
       <c r="R47" t="n">
-        <v>6665543</v>
+        <v>6665747</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126024179</v>
+        <v>126002194</v>
       </c>
       <c r="B48" t="n">
-        <v>75006</v>
+        <v>95687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630188</v>
+        <v>630166</v>
       </c>
       <c r="R48" t="n">
-        <v>6665726</v>
+        <v>6665496</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126002192</v>
+        <v>126024180</v>
       </c>
       <c r="B49" t="n">
-        <v>95687</v>
+        <v>75006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630144</v>
+        <v>630152</v>
       </c>
       <c r="R49" t="n">
-        <v>6665747</v>
+        <v>6665543</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126002194</v>
+        <v>126024179</v>
       </c>
       <c r="B50" t="n">
-        <v>95687</v>
+        <v>75006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630166</v>
+        <v>630188</v>
       </c>
       <c r="R50" t="n">
-        <v>6665496</v>
+        <v>6665726</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B4" t="n">
-        <v>96587</v>
+        <v>58506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R4" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -942,12 +947,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,50 +977,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B5" t="n">
-        <v>58506</v>
+        <v>96591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R5" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1044,18 +1050,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>75006</v>
+        <v>97009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,34 +1085,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R6" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,6 +1157,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>98978</v>
+        <v>75006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R7" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1268,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>97005</v>
+        <v>98982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,38 +1284,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R8" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1351,7 +1352,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002189</v>
+        <v>126002222</v>
       </c>
       <c r="B11" t="n">
-        <v>103765</v>
+        <v>95787</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630176</v>
+        <v>630048</v>
       </c>
       <c r="R11" t="n">
-        <v>6665491</v>
+        <v>6665785</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002222</v>
+        <v>126002225</v>
       </c>
       <c r="B12" t="n">
-        <v>95783</v>
+        <v>4778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,38 +1693,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630048</v>
+        <v>630146</v>
       </c>
       <c r="R12" t="n">
-        <v>6665785</v>
+        <v>6665497</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1754,18 +1755,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002220</v>
+        <v>126002189</v>
       </c>
       <c r="B13" t="n">
-        <v>75006</v>
+        <v>103769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1795,34 +1790,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630176</v>
       </c>
       <c r="R13" t="n">
-        <v>6665505</v>
+        <v>6665491</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1863,6 +1862,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002217</v>
+        <v>126002220</v>
       </c>
       <c r="B14" t="n">
         <v>75006</v>
@@ -1919,7 +1919,7 @@
         <v>630162</v>
       </c>
       <c r="R14" t="n">
-        <v>6665729</v>
+        <v>6665505</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1981,7 +1981,7 @@
         <v>126002185</v>
       </c>
       <c r="B15" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002225</v>
+        <v>126002217</v>
       </c>
       <c r="B16" t="n">
-        <v>4778</v>
+        <v>75006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R16" t="n">
-        <v>6665497</v>
+        <v>6665729</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2172,50 +2172,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>58506</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R17" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2250,18 +2245,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2385,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>58506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126024178</v>
+        <v>126002196</v>
       </c>
       <c r="B21" t="n">
-        <v>75006</v>
+        <v>98982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,37 +2590,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630163</v>
+        <v>630120</v>
       </c>
       <c r="R21" t="n">
-        <v>6665743</v>
+        <v>6665550</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2647,17 +2644,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2666,7 +2658,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2685,7 +2676,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B22" t="n">
         <v>75006</v>
@@ -2714,16 +2705,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R22" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2744,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2764,6 +2763,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
         <v>75006</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B24" t="n">
-        <v>98978</v>
+        <v>75006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,7 +2979,7 @@
         <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>103765</v>
+        <v>103769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B26" t="n">
-        <v>95783</v>
+        <v>91197</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R26" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3178,7 +3173,7 @@
         <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3272,10 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B28" t="n">
-        <v>91193</v>
+        <v>95787</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3278,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R28" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3343,6 +3338,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>96591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R29" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B30" t="n">
-        <v>96587</v>
+        <v>91232</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R30" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,7 +3663,7 @@
         <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,50 +3960,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126002172</v>
+        <v>126024162</v>
       </c>
       <c r="B35" t="n">
-        <v>58506</v>
+        <v>96591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630047</v>
+        <v>630074</v>
       </c>
       <c r="R35" t="n">
-        <v>6665787</v>
+        <v>6665750</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4030,17 +4025,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4049,7 +4039,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4068,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024162</v>
+        <v>126024163</v>
       </c>
       <c r="B36" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4103,10 +4092,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630074</v>
+        <v>630065</v>
       </c>
       <c r="R36" t="n">
-        <v>6665750</v>
+        <v>6665730</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4165,45 +4154,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024163</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>96587</v>
+        <v>58506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630065</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665730</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4230,12 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>97439</v>
+        <v>97443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024164</v>
+        <v>126002221</v>
       </c>
       <c r="B42" t="n">
-        <v>96587</v>
+        <v>75006</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630182</v>
+        <v>630152</v>
       </c>
       <c r="R42" t="n">
-        <v>6665719</v>
+        <v>6665501</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002181</v>
+        <v>126024164</v>
       </c>
       <c r="B43" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630057</v>
+        <v>630182</v>
       </c>
       <c r="R43" t="n">
-        <v>6665764</v>
+        <v>6665719</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002197</v>
+        <v>126002181</v>
       </c>
       <c r="B44" t="n">
-        <v>98978</v>
+        <v>96591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630142</v>
+        <v>630057</v>
       </c>
       <c r="R44" t="n">
-        <v>6665504</v>
+        <v>6665764</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4956,10 +4956,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126002221</v>
+        <v>126024182</v>
       </c>
       <c r="B45" t="n">
-        <v>75006</v>
+        <v>4778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,21 +4967,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630152</v>
+        <v>630146</v>
       </c>
       <c r="R45" t="n">
-        <v>6665501</v>
+        <v>6665537</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>4778</v>
+        <v>98982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R46" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5153,7 +5153,7 @@
         <v>126002192</v>
       </c>
       <c r="B47" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002194</v>
+        <v>126024180</v>
       </c>
       <c r="B48" t="n">
-        <v>95687</v>
+        <v>75006</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630166</v>
+        <v>630152</v>
       </c>
       <c r="R48" t="n">
-        <v>6665496</v>
+        <v>6665543</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,7 +5344,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024180</v>
+        <v>126024179</v>
       </c>
       <c r="B49" t="n">
         <v>75006</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630152</v>
+        <v>630188</v>
       </c>
       <c r="R49" t="n">
-        <v>6665543</v>
+        <v>6665726</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126024179</v>
+        <v>126002194</v>
       </c>
       <c r="B50" t="n">
-        <v>75006</v>
+        <v>95691</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630188</v>
+        <v>630166</v>
       </c>
       <c r="R50" t="n">
-        <v>6665726</v>
+        <v>6665496</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>58506</v>
+        <v>96591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R4" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -947,18 +942,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -977,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B5" t="n">
-        <v>96591</v>
+        <v>58506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R5" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1050,12 +1044,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B9" t="n">
-        <v>56597</v>
+        <v>58506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R9" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1443,12 +1448,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1467,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B10" t="n">
-        <v>58506</v>
+        <v>56597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,39 +1489,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R10" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1545,18 +1551,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B6" t="n">
-        <v>97009</v>
+        <v>98983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,38 +1085,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R6" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1157,7 +1153,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1176,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B7" t="n">
-        <v>75006</v>
+        <v>97010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,34 +1182,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R7" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1255,6 +1254,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B8" t="n">
-        <v>98982</v>
+        <v>75006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R8" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>58506</v>
+        <v>56597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,39 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R9" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1448,18 +1443,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>56597</v>
+        <v>58506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,34 +1478,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R10" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1551,12 +1545,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002222</v>
+        <v>126002220</v>
       </c>
       <c r="B11" t="n">
-        <v>95787</v>
+        <v>75006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,38 +1586,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R11" t="n">
-        <v>6665785</v>
+        <v>6665505</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1652,18 +1648,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1682,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002225</v>
+        <v>126002217</v>
       </c>
       <c r="B12" t="n">
-        <v>4778</v>
+        <v>75006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R12" t="n">
-        <v>6665497</v>
+        <v>6665729</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1779,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002189</v>
+        <v>126002222</v>
       </c>
       <c r="B13" t="n">
-        <v>103769</v>
+        <v>95788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1818,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630176</v>
+        <v>630048</v>
       </c>
       <c r="R13" t="n">
-        <v>6665491</v>
+        <v>6665785</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1854,6 +1844,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1881,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>75006</v>
+        <v>91197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1892,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R14" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002185</v>
+        <v>126002225</v>
       </c>
       <c r="B15" t="n">
-        <v>91197</v>
+        <v>4778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630050</v>
+        <v>630146</v>
       </c>
       <c r="R15" t="n">
-        <v>6665784</v>
+        <v>6665497</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002217</v>
+        <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>75006</v>
+        <v>103770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,34 +2081,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630162</v>
+        <v>630176</v>
       </c>
       <c r="R16" t="n">
-        <v>6665729</v>
+        <v>6665491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2154,6 +2153,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002227</v>
+        <v>126002191</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>57811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,34 +2183,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630081</v>
+        <v>630106</v>
       </c>
       <c r="R17" t="n">
-        <v>6665659</v>
+        <v>6665554</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2269,42 +2277,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>57811</v>
+        <v>58506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2355,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,50 +2385,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B19" t="n">
-        <v>58506</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002196</v>
+        <v>126024178</v>
       </c>
       <c r="B21" t="n">
-        <v>98982</v>
+        <v>75006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,34 +2590,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630120</v>
+        <v>630163</v>
       </c>
       <c r="R21" t="n">
-        <v>6665550</v>
+        <v>6665743</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2644,12 +2647,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,6 +2666,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024178</v>
+        <v>126002219</v>
       </c>
       <c r="B22" t="n">
         <v>75006</v>
@@ -2705,19 +2714,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630163</v>
+        <v>630108</v>
       </c>
       <c r="R22" t="n">
-        <v>6665743</v>
+        <v>6665515</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2744,17 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2763,7 +2764,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126024175</v>
       </c>
       <c r="B23" t="n">
         <v>75006</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630159</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665738</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75006</v>
+        <v>98983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,7 +2979,7 @@
         <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>103769</v>
+        <v>103770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>91197</v>
+        <v>95788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R26" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3173,7 +3178,7 @@
         <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3267,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B28" t="n">
-        <v>95787</v>
+        <v>91197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3278,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R28" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3338,11 +3343,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B29" t="n">
-        <v>96591</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R29" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>91232</v>
+        <v>96592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R30" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3663,7 +3663,7 @@
         <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024169</v>
+        <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>57648</v>
+        <v>96592</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,38 +3865,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630101</v>
+        <v>630074</v>
       </c>
       <c r="R34" t="n">
-        <v>6665757</v>
+        <v>6665750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3960,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024162</v>
+        <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3995,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630074</v>
+        <v>630065</v>
       </c>
       <c r="R35" t="n">
-        <v>6665750</v>
+        <v>6665730</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4057,45 +4048,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024163</v>
+        <v>126002172</v>
       </c>
       <c r="B36" t="n">
-        <v>96591</v>
+        <v>58506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630065</v>
+        <v>630047</v>
       </c>
       <c r="R36" t="n">
-        <v>6665730</v>
+        <v>6665787</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4122,12 +4118,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4136,6 +4137,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4154,36 +4156,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B37" t="n">
-        <v>58506</v>
+        <v>57648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4225,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002224</v>
+        <v>126002175</v>
       </c>
       <c r="B39" t="n">
-        <v>97443</v>
+        <v>58506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,34 +4370,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>569</v>
+        <v>208250</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630126</v>
+        <v>630182</v>
       </c>
       <c r="R39" t="n">
-        <v>6665560</v>
+        <v>6665478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4432,12 +4437,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B40" t="n">
-        <v>58506</v>
+        <v>97444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,39 +4478,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R40" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4534,18 +4540,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B42" t="n">
-        <v>75006</v>
+        <v>96592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R42" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126024164</v>
+        <v>126002181</v>
       </c>
       <c r="B43" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630182</v>
+        <v>630057</v>
       </c>
       <c r="R43" t="n">
-        <v>6665719</v>
+        <v>6665764</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002181</v>
+        <v>126002221</v>
       </c>
       <c r="B44" t="n">
-        <v>96591</v>
+        <v>75006</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630057</v>
+        <v>630152</v>
       </c>
       <c r="R44" t="n">
-        <v>6665764</v>
+        <v>6665501</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5056,7 +5056,7 @@
         <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>98982</v>
+        <v>98983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>126002192</v>
       </c>
       <c r="B47" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126024180</v>
+        <v>126002194</v>
       </c>
       <c r="B48" t="n">
-        <v>75006</v>
+        <v>95692</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630152</v>
+        <v>630166</v>
       </c>
       <c r="R48" t="n">
-        <v>6665543</v>
+        <v>6665496</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,7 +5344,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024179</v>
+        <v>126024180</v>
       </c>
       <c r="B49" t="n">
         <v>75006</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630188</v>
+        <v>630152</v>
       </c>
       <c r="R49" t="n">
-        <v>6665726</v>
+        <v>6665543</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126002194</v>
+        <v>126024179</v>
       </c>
       <c r="B50" t="n">
-        <v>95691</v>
+        <v>75006</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630166</v>
+        <v>630188</v>
       </c>
       <c r="R50" t="n">
-        <v>6665496</v>
+        <v>6665726</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B6" t="n">
-        <v>98983</v>
+        <v>75006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,21 +1085,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R6" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B7" t="n">
-        <v>97010</v>
+        <v>98983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,38 +1182,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R7" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1254,7 +1250,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B8" t="n">
-        <v>75006</v>
+        <v>97010</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,34 +1279,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R8" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1352,6 +1351,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002220</v>
+        <v>126002189</v>
       </c>
       <c r="B11" t="n">
-        <v>75006</v>
+        <v>103770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,34 +1586,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630162</v>
+        <v>630176</v>
       </c>
       <c r="R11" t="n">
-        <v>6665505</v>
+        <v>6665491</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1654,6 +1658,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1672,7 +1677,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002217</v>
+        <v>126002220</v>
       </c>
       <c r="B12" t="n">
         <v>75006</v>
@@ -1710,7 +1715,7 @@
         <v>630162</v>
       </c>
       <c r="R12" t="n">
-        <v>6665729</v>
+        <v>6665505</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002222</v>
+        <v>126002217</v>
       </c>
       <c r="B13" t="n">
-        <v>95788</v>
+        <v>75006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,38 +1785,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665785</v>
+        <v>6665729</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1846,18 +1847,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1876,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002185</v>
+        <v>126002222</v>
       </c>
       <c r="B14" t="n">
-        <v>91197</v>
+        <v>95788</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1882,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630050</v>
+        <v>630048</v>
       </c>
       <c r="R14" t="n">
-        <v>6665784</v>
+        <v>6665785</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1949,12 +1948,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1978,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002225</v>
+        <v>126002185</v>
       </c>
       <c r="B15" t="n">
-        <v>4778</v>
+        <v>91197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1989,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2013,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630146</v>
+        <v>630050</v>
       </c>
       <c r="R15" t="n">
-        <v>6665497</v>
+        <v>6665784</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2070,10 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002189</v>
+        <v>126002225</v>
       </c>
       <c r="B16" t="n">
-        <v>103770</v>
+        <v>4778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,38 +2086,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630176</v>
+        <v>630146</v>
       </c>
       <c r="R16" t="n">
-        <v>6665491</v>
+        <v>6665497</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2153,7 +2154,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B38" t="n">
-        <v>95692</v>
+        <v>58506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,34 +4273,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R38" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4332,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4341,6 +4351,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4359,10 +4370,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>58506</v>
+        <v>97444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,39 +4381,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R39" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4437,18 +4443,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B40" t="n">
-        <v>97444</v>
+        <v>95692</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R40" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4532,12 +4532,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002189</v>
+        <v>126002222</v>
       </c>
       <c r="B11" t="n">
-        <v>103770</v>
+        <v>95788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630176</v>
+        <v>630048</v>
       </c>
       <c r="R11" t="n">
-        <v>6665491</v>
+        <v>6665785</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B12" t="n">
-        <v>75006</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1712,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R12" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1774,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002217</v>
+        <v>126002225</v>
       </c>
       <c r="B13" t="n">
-        <v>75006</v>
+        <v>4778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1785,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1809,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630146</v>
       </c>
       <c r="R13" t="n">
-        <v>6665729</v>
+        <v>6665497</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1871,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002222</v>
+        <v>126002220</v>
       </c>
       <c r="B14" t="n">
-        <v>95788</v>
+        <v>75006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,38 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R14" t="n">
-        <v>6665785</v>
+        <v>6665505</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1948,18 +1949,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002185</v>
+        <v>126002217</v>
       </c>
       <c r="B15" t="n">
-        <v>91197</v>
+        <v>75006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R15" t="n">
-        <v>6665784</v>
+        <v>6665729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002225</v>
+        <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>4778</v>
+        <v>103770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,34 +2081,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630146</v>
+        <v>630176</v>
       </c>
       <c r="R16" t="n">
-        <v>6665497</v>
+        <v>6665491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2154,6 +2153,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>96592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R29" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,32 +3466,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126002180</v>
+        <v>126024176</v>
       </c>
       <c r="B30" t="n">
-        <v>96592</v>
+        <v>75006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630049</v>
+        <v>630066</v>
       </c>
       <c r="R30" t="n">
-        <v>6665789</v>
+        <v>6665750</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3563,32 +3563,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126024176</v>
+        <v>126024166</v>
       </c>
       <c r="B31" t="n">
-        <v>75006</v>
+        <v>91232</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630066</v>
+        <v>630159</v>
       </c>
       <c r="R31" t="n">
-        <v>6665750</v>
+        <v>6665490</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>95692</v>
+        <v>75006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R32" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>75006</v>
+        <v>95692</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R33" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,36 +4048,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>58506</v>
+        <v>57648</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4088,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4118,17 +4117,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4137,7 +4136,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,35 +4154,36 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>57648</v>
+        <v>58506</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4195,10 +4194,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4225,17 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002218</v>
       </c>
       <c r="B2" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002215</v>
       </c>
       <c r="B3" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126002174</v>
       </c>
       <c r="B5" t="n">
-        <v>58506</v>
+        <v>58507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>75006</v>
+        <v>97012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,34 +1085,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R6" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,6 +1157,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>98983</v>
+        <v>75007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R7" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1268,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>97010</v>
+        <v>98985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,38 +1284,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R8" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1351,7 +1352,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>58506</v>
+        <v>58507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002222</v>
+        <v>126002189</v>
       </c>
       <c r="B11" t="n">
-        <v>95788</v>
+        <v>103772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630048</v>
+        <v>630176</v>
       </c>
       <c r="R11" t="n">
-        <v>6665785</v>
+        <v>6665491</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,11 +1650,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,10 +1677,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002185</v>
+        <v>126002222</v>
       </c>
       <c r="B12" t="n">
-        <v>91197</v>
+        <v>95790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,34 +1688,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630050</v>
+        <v>630048</v>
       </c>
       <c r="R12" t="n">
-        <v>6665784</v>
+        <v>6665785</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1755,12 +1754,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1779,10 +1784,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002225</v>
+        <v>126002220</v>
       </c>
       <c r="B13" t="n">
-        <v>4778</v>
+        <v>75007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1795,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665497</v>
+        <v>6665505</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1876,10 +1881,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>75006</v>
+        <v>91199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1892,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R14" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1976,7 +1981,7 @@
         <v>126002217</v>
       </c>
       <c r="B15" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002189</v>
+        <v>126002225</v>
       </c>
       <c r="B16" t="n">
-        <v>103770</v>
+        <v>4778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,38 +2086,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630176</v>
+        <v>630146</v>
       </c>
       <c r="R16" t="n">
-        <v>6665491</v>
+        <v>6665497</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2153,7 +2154,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002191</v>
+        <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>57811</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,42 +2183,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630106</v>
+        <v>630081</v>
       </c>
       <c r="R17" t="n">
-        <v>6665554</v>
+        <v>6665659</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,39 +2269,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B18" t="n">
-        <v>58506</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2317,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R18" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2355,18 +2350,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2385,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>58507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002178</v>
+        <v>126002196</v>
       </c>
       <c r="B20" t="n">
-        <v>96592</v>
+        <v>98985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630009</v>
+        <v>630120</v>
       </c>
       <c r="R20" t="n">
-        <v>6665706</v>
+        <v>6665550</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2579,48 +2579,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126024178</v>
+        <v>126002178</v>
       </c>
       <c r="B21" t="n">
-        <v>75006</v>
+        <v>96594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630163</v>
+        <v>630009</v>
       </c>
       <c r="R21" t="n">
-        <v>6665743</v>
+        <v>6665706</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2642,22 +2639,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2666,7 +2658,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2685,10 +2676,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B22" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2714,16 +2705,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R22" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2744,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2764,6 +2763,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B24" t="n">
-        <v>98983</v>
+        <v>75007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2979,7 +2979,7 @@
         <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>103770</v>
+        <v>103772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>126002184</v>
       </c>
       <c r="B28" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3466,32 +3466,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024176</v>
+        <v>126024166</v>
       </c>
       <c r="B30" t="n">
-        <v>75006</v>
+        <v>91234</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630066</v>
+        <v>630159</v>
       </c>
       <c r="R30" t="n">
-        <v>6665750</v>
+        <v>6665490</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3563,32 +3563,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126024166</v>
+        <v>126024176</v>
       </c>
       <c r="B31" t="n">
-        <v>91232</v>
+        <v>75007</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630159</v>
+        <v>630066</v>
       </c>
       <c r="R31" t="n">
-        <v>6665490</v>
+        <v>6665750</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3663,7 +3663,7 @@
         <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,35 +4048,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B36" t="n">
-        <v>57648</v>
+        <v>58507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4087,10 +4088,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4117,17 +4118,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4136,6 +4137,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4154,36 +4156,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B37" t="n">
-        <v>58506</v>
+        <v>57649</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4225,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B38" t="n">
-        <v>58506</v>
+        <v>97446</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,39 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R38" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4340,18 +4335,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4370,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>97444</v>
+        <v>95694</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4405,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R39" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4435,12 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4467,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>95692</v>
+        <v>58507</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,34 +4467,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R40" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4532,12 +4526,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4546,6 +4545,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>126002213</v>
       </c>
       <c r="B41" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>126024164</v>
       </c>
       <c r="B42" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>126002181</v>
       </c>
       <c r="B43" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002221</v>
+        <v>126024182</v>
       </c>
       <c r="B44" t="n">
-        <v>75006</v>
+        <v>4778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,21 +4870,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630152</v>
+        <v>630146</v>
       </c>
       <c r="R44" t="n">
-        <v>6665501</v>
+        <v>6665537</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,10 +4956,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024182</v>
+        <v>126002221</v>
       </c>
       <c r="B45" t="n">
-        <v>4778</v>
+        <v>75007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4967,21 +4967,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630146</v>
+        <v>630152</v>
       </c>
       <c r="R45" t="n">
-        <v>6665537</v>
+        <v>6665501</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5056,7 +5056,7 @@
         <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>98983</v>
+        <v>98985</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126002192</v>
+        <v>126024180</v>
       </c>
       <c r="B47" t="n">
-        <v>95692</v>
+        <v>75007</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630144</v>
+        <v>630152</v>
       </c>
       <c r="R47" t="n">
-        <v>6665747</v>
+        <v>6665543</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002194</v>
+        <v>126002192</v>
       </c>
       <c r="B48" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630166</v>
+        <v>630144</v>
       </c>
       <c r="R48" t="n">
-        <v>6665496</v>
+        <v>6665747</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024180</v>
+        <v>126024179</v>
       </c>
       <c r="B49" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630152</v>
+        <v>630188</v>
       </c>
       <c r="R49" t="n">
-        <v>6665543</v>
+        <v>6665726</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126024179</v>
+        <v>126002194</v>
       </c>
       <c r="B50" t="n">
-        <v>75006</v>
+        <v>95694</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630188</v>
+        <v>630166</v>
       </c>
       <c r="R50" t="n">
-        <v>6665726</v>
+        <v>6665496</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002189</v>
+        <v>126002222</v>
       </c>
       <c r="B11" t="n">
-        <v>103772</v>
+        <v>95790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,21 +1586,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630176</v>
+        <v>630048</v>
       </c>
       <c r="R11" t="n">
-        <v>6665491</v>
+        <v>6665785</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1650,6 +1650,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002222</v>
+        <v>126002220</v>
       </c>
       <c r="B12" t="n">
-        <v>95790</v>
+        <v>75007</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,38 +1693,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R12" t="n">
-        <v>6665785</v>
+        <v>6665505</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1754,18 +1755,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B13" t="n">
-        <v>75007</v>
+        <v>91199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1795,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1819,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R13" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1881,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002185</v>
+        <v>126002217</v>
       </c>
       <c r="B14" t="n">
-        <v>91199</v>
+        <v>75007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1892,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1916,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R14" t="n">
-        <v>6665784</v>
+        <v>6665729</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1978,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002217</v>
+        <v>126002225</v>
       </c>
       <c r="B15" t="n">
-        <v>75007</v>
+        <v>4778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1989,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2013,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630162</v>
+        <v>630146</v>
       </c>
       <c r="R15" t="n">
-        <v>6665729</v>
+        <v>6665497</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002225</v>
+        <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>4778</v>
+        <v>103772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,34 +2081,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630146</v>
+        <v>630176</v>
       </c>
       <c r="R16" t="n">
-        <v>6665497</v>
+        <v>6665491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2154,6 +2153,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002190</v>
+        <v>126002193</v>
       </c>
       <c r="B25" t="n">
-        <v>103772</v>
+        <v>95694</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630188</v>
+        <v>630171</v>
       </c>
       <c r="R25" t="n">
-        <v>6665482</v>
+        <v>6665468</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B26" t="n">
-        <v>95790</v>
+        <v>91199</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R26" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B27" t="n">
-        <v>95694</v>
+        <v>103772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3181,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R27" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3272,10 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B28" t="n">
-        <v>91199</v>
+        <v>95790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3278,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R28" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3343,6 +3338,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024162</v>
+        <v>126024169</v>
       </c>
       <c r="B34" t="n">
-        <v>96594</v>
+        <v>57649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,34 +3865,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630074</v>
+        <v>630101</v>
       </c>
       <c r="R34" t="n">
-        <v>6665750</v>
+        <v>6665757</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3925,6 +3929,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,7 +3960,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024163</v>
+        <v>126024162</v>
       </c>
       <c r="B35" t="n">
         <v>96594</v>
@@ -3986,10 +3995,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630065</v>
+        <v>630074</v>
       </c>
       <c r="R35" t="n">
-        <v>6665730</v>
+        <v>6665750</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4048,50 +4057,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126002172</v>
+        <v>126024163</v>
       </c>
       <c r="B36" t="n">
-        <v>58507</v>
+        <v>96594</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630047</v>
+        <v>630065</v>
       </c>
       <c r="R36" t="n">
-        <v>6665787</v>
+        <v>6665730</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4118,17 +4122,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4137,7 +4136,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,35 +4154,36 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>57649</v>
+        <v>58507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4195,10 +4194,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4225,17 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>97446</v>
+        <v>95694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>95694</v>
+        <v>97446</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R39" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024164</v>
+        <v>126002221</v>
       </c>
       <c r="B42" t="n">
-        <v>96594</v>
+        <v>75007</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630182</v>
+        <v>630152</v>
       </c>
       <c r="R42" t="n">
-        <v>6665719</v>
+        <v>6665501</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B43" t="n">
-        <v>96594</v>
+        <v>4778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R43" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,10 +4859,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B44" t="n">
-        <v>4778</v>
+        <v>98985</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,21 +4870,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R44" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B45" t="n">
-        <v>75007</v>
+        <v>96594</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R45" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002197</v>
+        <v>126002181</v>
       </c>
       <c r="B46" t="n">
-        <v>98985</v>
+        <v>96594</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630142</v>
+        <v>630057</v>
       </c>
       <c r="R46" t="n">
-        <v>6665504</v>
+        <v>6665764</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5536,6 +5536,2015 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126217641</v>
+      </c>
+      <c r="B51" t="n">
+        <v>84963</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>241</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>630167</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6665576</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126218973</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80630</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>630143</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6665544</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126217611</v>
+      </c>
+      <c r="B53" t="n">
+        <v>95696</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>630169</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6665581</v>
+      </c>
+      <c r="S53" t="n">
+        <v>12</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126217596</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>630144</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6665539</v>
+      </c>
+      <c r="S54" t="n">
+        <v>12</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126217606</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>630144</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6665539</v>
+      </c>
+      <c r="S55" t="n">
+        <v>12</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På stående högstubbe av gran med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126218961</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>630158</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6665746</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>död ask</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126217645</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>630136</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6665602</v>
+      </c>
+      <c r="S57" t="n">
+        <v>12</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126217612</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>630167</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6665616</v>
+      </c>
+      <c r="S58" t="n">
+        <v>12</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126217608</v>
+      </c>
+      <c r="B59" t="n">
+        <v>103774</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>630187</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6665511</v>
+      </c>
+      <c r="S59" t="n">
+        <v>12</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126218957</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80036</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>630091</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6665780</v>
+      </c>
+      <c r="S60" t="n">
+        <v>20</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126218955</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80076</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>630083</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6665774</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>liggande ask</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126218954</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79353</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6431</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bacidia rubella</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>630052</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6665775</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126218969</v>
+      </c>
+      <c r="B63" t="n">
+        <v>96596</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>630165</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6665579</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126217633</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80076</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>630145</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6665541</v>
+      </c>
+      <c r="S64" t="n">
+        <v>12</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126217629</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>630175</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6665531</v>
+      </c>
+      <c r="S65" t="n">
+        <v>12</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Stor fruktkropp på undersidan av ganska murken granlåga i en av de många blötare delarna av gransumpskogen. Luktar parmesan, speciellt efter att den legat i en kollektlåda. Kollekt är insamlad (men inte av mig).</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126218977</v>
+      </c>
+      <c r="B66" t="n">
+        <v>75007</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>630153</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6665493</v>
+      </c>
+      <c r="S66" t="n">
+        <v>20</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126218972</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79482</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>630143</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6665544</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126218979</v>
+      </c>
+      <c r="B68" t="n">
+        <v>74879</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Liljansberg, skogsområde S om, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>630168</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6665514</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126217639</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80630</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>630145</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6665542</v>
+      </c>
+      <c r="S69" t="n">
+        <v>12</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126217643</v>
+      </c>
+      <c r="B70" t="n">
+        <v>97448</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>569</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gogubbkärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>630122</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6665560</v>
+      </c>
+      <c r="S70" t="n">
+        <v>12</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>97012</v>
+        <v>97014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>98985</v>
+        <v>98987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002222</v>
+        <v>126002185</v>
       </c>
       <c r="B11" t="n">
-        <v>95790</v>
+        <v>91201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,38 +1586,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630048</v>
+        <v>630050</v>
       </c>
       <c r="R11" t="n">
-        <v>6665785</v>
+        <v>6665784</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1652,18 +1648,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1779,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002185</v>
+        <v>126002217</v>
       </c>
       <c r="B13" t="n">
-        <v>91199</v>
+        <v>75007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665784</v>
+        <v>6665729</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1876,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002217</v>
+        <v>126002189</v>
       </c>
       <c r="B14" t="n">
-        <v>75007</v>
+        <v>103774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1877,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630162</v>
+        <v>630176</v>
       </c>
       <c r="R14" t="n">
-        <v>6665729</v>
+        <v>6665491</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,6 +1949,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002225</v>
+        <v>126002222</v>
       </c>
       <c r="B15" t="n">
-        <v>4778</v>
+        <v>95792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,34 +1979,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630146</v>
+        <v>630048</v>
       </c>
       <c r="R15" t="n">
-        <v>6665497</v>
+        <v>6665785</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2046,12 +2045,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2070,10 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002189</v>
+        <v>126002225</v>
       </c>
       <c r="B16" t="n">
-        <v>103772</v>
+        <v>4778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,38 +2086,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630176</v>
+        <v>630146</v>
       </c>
       <c r="R16" t="n">
-        <v>6665491</v>
+        <v>6665497</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2153,7 +2154,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2269,42 +2269,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>58507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2309,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2347,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,39 +2377,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B19" t="n">
-        <v>58507</v>
+        <v>57812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2414,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002196</v>
+        <v>126024178</v>
       </c>
       <c r="B20" t="n">
-        <v>98985</v>
+        <v>75007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,34 +2493,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630120</v>
+        <v>630163</v>
       </c>
       <c r="R20" t="n">
-        <v>6665550</v>
+        <v>6665743</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2547,12 +2550,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,6 +2569,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2579,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002178</v>
+        <v>126002219</v>
       </c>
       <c r="B21" t="n">
-        <v>96594</v>
+        <v>75007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2614,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630009</v>
+        <v>630108</v>
       </c>
       <c r="R21" t="n">
-        <v>6665706</v>
+        <v>6665515</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2639,7 +2648,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2676,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024178</v>
+        <v>126024175</v>
       </c>
       <c r="B22" t="n">
         <v>75007</v>
@@ -2705,19 +2714,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630163</v>
+        <v>630159</v>
       </c>
       <c r="R22" t="n">
-        <v>6665743</v>
+        <v>6665738</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2752,18 +2758,12 @@
           <t>2025-06-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126002178</v>
       </c>
       <c r="B23" t="n">
-        <v>75007</v>
+        <v>96596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630009</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665706</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75007</v>
+        <v>98987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>95694</v>
+        <v>103774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R25" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>91199</v>
+        <v>95792</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R26" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002190</v>
+        <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>103772</v>
+        <v>95696</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3205,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630188</v>
+        <v>630171</v>
       </c>
       <c r="R27" t="n">
-        <v>6665482</v>
+        <v>6665468</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3267,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B28" t="n">
-        <v>95790</v>
+        <v>91201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3278,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R28" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3338,11 +3343,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B29" t="n">
-        <v>96594</v>
+        <v>91236</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R29" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>91234</v>
+        <v>96596</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R30" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>75007</v>
+        <v>95696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R32" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B33" t="n">
-        <v>95694</v>
+        <v>75007</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R33" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024169</v>
+        <v>126024163</v>
       </c>
       <c r="B34" t="n">
-        <v>57649</v>
+        <v>96596</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,38 +3865,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630101</v>
+        <v>630065</v>
       </c>
       <c r="R34" t="n">
-        <v>6665757</v>
+        <v>6665730</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3963,7 +3954,7 @@
         <v>126024162</v>
       </c>
       <c r="B35" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024163</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>96594</v>
+        <v>57649</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,34 +4059,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630065</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665730</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4128,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B38" t="n">
-        <v>95694</v>
+        <v>97448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R38" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>97446</v>
+        <v>95696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R39" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4862,7 +4862,7 @@
         <v>126002197</v>
       </c>
       <c r="B44" t="n">
-        <v>98985</v>
+        <v>98987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4956,10 +4956,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024164</v>
+        <v>126002181</v>
       </c>
       <c r="B45" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630182</v>
+        <v>630057</v>
       </c>
       <c r="R45" t="n">
-        <v>6665719</v>
+        <v>6665764</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002181</v>
+        <v>126024164</v>
       </c>
       <c r="B46" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630057</v>
+        <v>630182</v>
       </c>
       <c r="R46" t="n">
-        <v>6665764</v>
+        <v>6665719</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002192</v>
+        <v>126024179</v>
       </c>
       <c r="B48" t="n">
-        <v>95694</v>
+        <v>75007</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630144</v>
+        <v>630188</v>
       </c>
       <c r="R48" t="n">
-        <v>6665747</v>
+        <v>6665726</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024179</v>
+        <v>126002192</v>
       </c>
       <c r="B49" t="n">
-        <v>75007</v>
+        <v>95696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630188</v>
+        <v>630144</v>
       </c>
       <c r="R49" t="n">
-        <v>6665726</v>
+        <v>6665747</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5444,7 +5444,7 @@
         <v>126002194</v>
       </c>
       <c r="B50" t="n">
-        <v>95694</v>
+        <v>95696</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5931,48 +5931,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126217606</v>
+        <v>126218961</v>
       </c>
       <c r="B55" t="n">
-        <v>91236</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630144</v>
+        <v>630158</v>
       </c>
       <c r="R55" t="n">
-        <v>6665539</v>
+        <v>6665746</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6004,11 +6004,6 @@
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På stående högstubbe av gran med barken kvar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6017,64 +6012,69 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>död ask</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126218961</v>
+        <v>126217606</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>91236</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1026</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630158</v>
+        <v>630144</v>
       </c>
       <c r="R56" t="n">
-        <v>6665746</v>
+        <v>6665539</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6106,6 +6106,11 @@
           <t>2025-06-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På stående högstubbe av gran med barken kvar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6114,21 +6119,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>död ask</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6225,7 +6225,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6640,32 +6640,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126218954</v>
+        <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>79353</v>
+        <v>96596</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6431</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630052</v>
+        <v>630165</v>
       </c>
       <c r="R62" t="n">
-        <v>6665775</v>
+        <v>6665579</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126218969</v>
+        <v>126218954</v>
       </c>
       <c r="B63" t="n">
-        <v>96596</v>
+        <v>79353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6431</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630165</v>
+        <v>630052</v>
       </c>
       <c r="R63" t="n">
-        <v>6665579</v>
+        <v>6665775</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2269,39 +2269,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B18" t="n">
-        <v>58507</v>
+        <v>57812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2309,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R18" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2347,18 +2350,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2377,42 +2374,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>57812</v>
+        <v>58507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2420,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002221</v>
+        <v>126002181</v>
       </c>
       <c r="B42" t="n">
-        <v>75007</v>
+        <v>96596</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630152</v>
+        <v>630057</v>
       </c>
       <c r="R42" t="n">
-        <v>6665501</v>
+        <v>6665764</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126024182</v>
+        <v>126024164</v>
       </c>
       <c r="B43" t="n">
-        <v>4778</v>
+        <v>96596</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630146</v>
+        <v>630182</v>
       </c>
       <c r="R43" t="n">
-        <v>6665537</v>
+        <v>6665719</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002197</v>
+        <v>126002221</v>
       </c>
       <c r="B44" t="n">
-        <v>98987</v>
+        <v>75007</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4870,21 +4870,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630142</v>
+        <v>630152</v>
       </c>
       <c r="R44" t="n">
-        <v>6665504</v>
+        <v>6665501</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B45" t="n">
-        <v>96596</v>
+        <v>4778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R45" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126024164</v>
+        <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>96596</v>
+        <v>98987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630182</v>
+        <v>630142</v>
       </c>
       <c r="R46" t="n">
-        <v>6665719</v>
+        <v>6665504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5737,32 +5737,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126217611</v>
+        <v>126217596</v>
       </c>
       <c r="B53" t="n">
-        <v>95696</v>
+        <v>79482</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2818</v>
+        <v>1026</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630169</v>
+        <v>630144</v>
       </c>
       <c r="R53" t="n">
-        <v>6665581</v>
+        <v>6665539</v>
       </c>
       <c r="S53" t="n">
         <v>12</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126217596</v>
+        <v>126217611</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>95696</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1026</v>
+        <v>2818</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630144</v>
+        <v>630169</v>
       </c>
       <c r="R54" t="n">
-        <v>6665539</v>
+        <v>6665581</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -7545,6 +7545,394 @@
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126266843</v>
+      </c>
+      <c r="B71" t="n">
+        <v>96598</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>630181</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6665656</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126266866</v>
+      </c>
+      <c r="B72" t="n">
+        <v>105931</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>630155</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6665736</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126266848</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98989</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222302</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spädstarr</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carex disperma</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Dewey</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>630135</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6665592</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126266859</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97450</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>569</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>630084</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6665754</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B4" t="n">
-        <v>96596</v>
+        <v>58507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R4" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -942,12 +947,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,50 +977,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B5" t="n">
-        <v>58507</v>
+        <v>96598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R5" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1044,18 +1050,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>97014</v>
+        <v>97016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>98987</v>
+        <v>98989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002185</v>
+        <v>126002222</v>
       </c>
       <c r="B11" t="n">
-        <v>91201</v>
+        <v>95794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,34 +1586,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630050</v>
+        <v>630048</v>
       </c>
       <c r="R11" t="n">
-        <v>6665784</v>
+        <v>6665785</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1648,12 +1652,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002217</v>
+        <v>126002185</v>
       </c>
       <c r="B13" t="n">
-        <v>75007</v>
+        <v>91203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R13" t="n">
-        <v>6665729</v>
+        <v>6665784</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1866,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002189</v>
+        <v>126002217</v>
       </c>
       <c r="B14" t="n">
-        <v>103774</v>
+        <v>75007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,38 +1887,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630176</v>
+        <v>630162</v>
       </c>
       <c r="R14" t="n">
-        <v>6665491</v>
+        <v>6665729</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1949,7 +1955,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002222</v>
+        <v>126002225</v>
       </c>
       <c r="B15" t="n">
-        <v>95792</v>
+        <v>4778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,38 +1984,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630048</v>
+        <v>630146</v>
       </c>
       <c r="R15" t="n">
-        <v>6665785</v>
+        <v>6665497</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2045,18 +2046,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002225</v>
+        <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>4778</v>
+        <v>103778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,34 +2081,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630146</v>
+        <v>630176</v>
       </c>
       <c r="R16" t="n">
-        <v>6665497</v>
+        <v>6665491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2154,6 +2153,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126024178</v>
+        <v>126002196</v>
       </c>
       <c r="B20" t="n">
-        <v>75007</v>
+        <v>98989</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,37 +2493,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630163</v>
+        <v>630120</v>
       </c>
       <c r="R20" t="n">
-        <v>6665743</v>
+        <v>6665550</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,17 +2547,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2569,7 +2561,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2588,32 +2579,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002219</v>
+        <v>126002178</v>
       </c>
       <c r="B21" t="n">
-        <v>75007</v>
+        <v>96598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2614,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630108</v>
+        <v>630009</v>
       </c>
       <c r="R21" t="n">
-        <v>6665515</v>
+        <v>6665706</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2648,7 +2639,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2685,7 +2676,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024175</v>
+        <v>126024178</v>
       </c>
       <c r="B22" t="n">
         <v>75007</v>
@@ -2714,16 +2705,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630159</v>
+        <v>630163</v>
       </c>
       <c r="R22" t="n">
-        <v>6665738</v>
+        <v>6665743</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2758,12 +2752,18 @@
           <t>2025-06-14</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002178</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
-        <v>96596</v>
+        <v>75007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630009</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665706</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B24" t="n">
-        <v>98987</v>
+        <v>75007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002190</v>
+        <v>126002193</v>
       </c>
       <c r="B25" t="n">
-        <v>103774</v>
+        <v>95698</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630188</v>
+        <v>630171</v>
       </c>
       <c r="R25" t="n">
-        <v>6665482</v>
+        <v>6665468</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B26" t="n">
-        <v>95792</v>
+        <v>91203</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R26" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B27" t="n">
-        <v>95696</v>
+        <v>103778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3181,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R27" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3272,10 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B28" t="n">
-        <v>91201</v>
+        <v>95794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3278,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3302,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R28" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3343,6 +3338,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3372,7 +3372,7 @@
         <v>126024166</v>
       </c>
       <c r="B29" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>95696</v>
+        <v>75007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R32" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>75007</v>
+        <v>95698</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R33" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024163</v>
+        <v>126024169</v>
       </c>
       <c r="B34" t="n">
-        <v>96596</v>
+        <v>57649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,34 +3865,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630065</v>
+        <v>630101</v>
       </c>
       <c r="R34" t="n">
-        <v>6665730</v>
+        <v>6665757</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3925,6 +3929,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3951,10 +3960,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024162</v>
+        <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3986,10 +3995,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630074</v>
+        <v>630065</v>
       </c>
       <c r="R35" t="n">
-        <v>6665750</v>
+        <v>6665730</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4048,10 +4057,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126024162</v>
       </c>
       <c r="B36" t="n">
-        <v>57649</v>
+        <v>96598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,38 +4068,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630074</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665750</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4123,11 +4128,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002224</v>
+        <v>126002175</v>
       </c>
       <c r="B38" t="n">
-        <v>97448</v>
+        <v>58507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,34 +4273,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>569</v>
+        <v>208250</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630126</v>
+        <v>630182</v>
       </c>
       <c r="R38" t="n">
-        <v>6665560</v>
+        <v>6665478</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4335,12 +4340,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4359,10 +4370,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>95696</v>
+        <v>97450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4381,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4405,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R39" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4435,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4456,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002175</v>
+        <v>126024167</v>
       </c>
       <c r="B40" t="n">
-        <v>58507</v>
+        <v>95698</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,39 +4478,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>2818</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630182</v>
+        <v>630055</v>
       </c>
       <c r="R40" t="n">
-        <v>6665478</v>
+        <v>6665749</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4526,17 +4532,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4545,7 +4546,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B42" t="n">
-        <v>96596</v>
+        <v>4778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R42" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126024164</v>
+        <v>126002197</v>
       </c>
       <c r="B43" t="n">
-        <v>96596</v>
+        <v>98989</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630182</v>
+        <v>630142</v>
       </c>
       <c r="R43" t="n">
-        <v>6665719</v>
+        <v>6665504</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002221</v>
+        <v>126002181</v>
       </c>
       <c r="B44" t="n">
-        <v>75007</v>
+        <v>96598</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630152</v>
+        <v>630057</v>
       </c>
       <c r="R44" t="n">
-        <v>6665501</v>
+        <v>6665764</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024182</v>
+        <v>126024164</v>
       </c>
       <c r="B45" t="n">
-        <v>4778</v>
+        <v>96598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630146</v>
+        <v>630182</v>
       </c>
       <c r="R45" t="n">
-        <v>6665537</v>
+        <v>6665719</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002197</v>
+        <v>126002221</v>
       </c>
       <c r="B46" t="n">
-        <v>98987</v>
+        <v>75007</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630142</v>
+        <v>630152</v>
       </c>
       <c r="R46" t="n">
-        <v>6665504</v>
+        <v>6665501</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126024180</v>
+        <v>126002192</v>
       </c>
       <c r="B47" t="n">
-        <v>75007</v>
+        <v>95698</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630152</v>
+        <v>630144</v>
       </c>
       <c r="R47" t="n">
-        <v>6665543</v>
+        <v>6665747</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126024179</v>
+        <v>126002194</v>
       </c>
       <c r="B48" t="n">
-        <v>75007</v>
+        <v>95698</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630188</v>
+        <v>630166</v>
       </c>
       <c r="R48" t="n">
-        <v>6665726</v>
+        <v>6665496</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126002192</v>
+        <v>126024180</v>
       </c>
       <c r="B49" t="n">
-        <v>95696</v>
+        <v>75007</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630144</v>
+        <v>630152</v>
       </c>
       <c r="R49" t="n">
-        <v>6665747</v>
+        <v>6665543</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126002194</v>
+        <v>126024179</v>
       </c>
       <c r="B50" t="n">
-        <v>95696</v>
+        <v>75007</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630166</v>
+        <v>630188</v>
       </c>
       <c r="R50" t="n">
-        <v>6665496</v>
+        <v>6665726</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5541,7 +5541,7 @@
         <v>126217641</v>
       </c>
       <c r="B51" t="n">
-        <v>84963</v>
+        <v>84964</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>126217611</v>
       </c>
       <c r="B54" t="n">
-        <v>95696</v>
+        <v>95698</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>126217606</v>
       </c>
       <c r="B56" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>126217645</v>
       </c>
       <c r="B57" t="n">
-        <v>97014</v>
+        <v>97016</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B58" t="n">
-        <v>57649</v>
+        <v>103778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R58" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B59" t="n">
-        <v>103774</v>
+        <v>57649</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R59" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6643,7 +6643,7 @@
         <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>126217629</v>
       </c>
       <c r="B65" t="n">
-        <v>91605</v>
+        <v>91607</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126217643</v>
       </c>
       <c r="B70" t="n">
-        <v>97448</v>
+        <v>97450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002220</v>
+        <v>126002225</v>
       </c>
       <c r="B12" t="n">
-        <v>75007</v>
+        <v>4778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630162</v>
+        <v>630146</v>
       </c>
       <c r="R12" t="n">
-        <v>6665505</v>
+        <v>6665497</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002185</v>
+        <v>126002220</v>
       </c>
       <c r="B13" t="n">
-        <v>91203</v>
+        <v>75007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665784</v>
+        <v>6665505</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002217</v>
+        <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>75007</v>
+        <v>91203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R14" t="n">
-        <v>6665729</v>
+        <v>6665784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002225</v>
+        <v>126002217</v>
       </c>
       <c r="B15" t="n">
-        <v>4778</v>
+        <v>75007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R15" t="n">
-        <v>6665497</v>
+        <v>6665729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2482,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002196</v>
+        <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>98989</v>
+        <v>96598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630120</v>
+        <v>630009</v>
       </c>
       <c r="R20" t="n">
-        <v>6665550</v>
+        <v>6665706</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2579,45 +2579,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002178</v>
+        <v>126024178</v>
       </c>
       <c r="B21" t="n">
-        <v>96598</v>
+        <v>75007</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630009</v>
+        <v>630163</v>
       </c>
       <c r="R21" t="n">
-        <v>6665706</v>
+        <v>6665743</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2639,17 +2642,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,6 +2666,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024178</v>
+        <v>126002219</v>
       </c>
       <c r="B22" t="n">
         <v>75007</v>
@@ -2705,19 +2714,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630163</v>
+        <v>630108</v>
       </c>
       <c r="R22" t="n">
-        <v>6665743</v>
+        <v>6665515</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2744,17 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2763,7 +2764,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126024175</v>
       </c>
       <c r="B23" t="n">
         <v>75007</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630159</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665738</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75007</v>
+        <v>98989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>95698</v>
+        <v>103778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R25" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002190</v>
+        <v>126002223</v>
       </c>
       <c r="B27" t="n">
-        <v>103778</v>
+        <v>95794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,21 +3181,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3205,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630188</v>
+        <v>630173</v>
       </c>
       <c r="R27" t="n">
-        <v>6665482</v>
+        <v>6665473</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3241,6 +3241,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3267,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002223</v>
+        <v>126002193</v>
       </c>
       <c r="B28" t="n">
-        <v>95794</v>
+        <v>95698</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3278,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3302,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630173</v>
+        <v>630171</v>
       </c>
       <c r="R28" t="n">
-        <v>6665473</v>
+        <v>6665468</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3338,11 +3343,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>75007</v>
+        <v>95698</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R32" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B33" t="n">
-        <v>95698</v>
+        <v>75007</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R33" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4665,10 +4665,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B42" t="n">
-        <v>4778</v>
+        <v>98989</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R42" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002197</v>
+        <v>126002181</v>
       </c>
       <c r="B43" t="n">
-        <v>98989</v>
+        <v>96598</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630142</v>
+        <v>630057</v>
       </c>
       <c r="R43" t="n">
-        <v>6665504</v>
+        <v>6665764</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002181</v>
+        <v>126024164</v>
       </c>
       <c r="B44" t="n">
         <v>96598</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630057</v>
+        <v>630182</v>
       </c>
       <c r="R44" t="n">
-        <v>6665764</v>
+        <v>6665719</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024164</v>
+        <v>126002221</v>
       </c>
       <c r="B45" t="n">
-        <v>96598</v>
+        <v>75007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630182</v>
+        <v>630152</v>
       </c>
       <c r="R45" t="n">
-        <v>6665719</v>
+        <v>6665501</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002221</v>
+        <v>126024182</v>
       </c>
       <c r="B46" t="n">
-        <v>75007</v>
+        <v>4778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630152</v>
+        <v>630146</v>
       </c>
       <c r="R46" t="n">
-        <v>6665501</v>
+        <v>6665537</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B58" t="n">
-        <v>103778</v>
+        <v>57649</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R58" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B59" t="n">
-        <v>57649</v>
+        <v>103778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R59" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002218</v>
       </c>
       <c r="B2" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002215</v>
       </c>
       <c r="B3" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126002174</v>
       </c>
       <c r="B4" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>126002179</v>
       </c>
       <c r="B5" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>97016</v>
+        <v>97020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>98989</v>
+        <v>98993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>56598</v>
+        <v>56602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002222</v>
+        <v>126002220</v>
       </c>
       <c r="B11" t="n">
-        <v>95794</v>
+        <v>75011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,38 +1586,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R11" t="n">
-        <v>6665785</v>
+        <v>6665505</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1652,18 +1648,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1682,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002225</v>
+        <v>126002217</v>
       </c>
       <c r="B12" t="n">
-        <v>4778</v>
+        <v>75011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R12" t="n">
-        <v>6665497</v>
+        <v>6665729</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1779,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002220</v>
+        <v>126002222</v>
       </c>
       <c r="B13" t="n">
-        <v>75007</v>
+        <v>95798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,34 +1780,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630048</v>
       </c>
       <c r="R13" t="n">
-        <v>6665505</v>
+        <v>6665785</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1852,12 +1846,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002217</v>
+        <v>126002225</v>
       </c>
       <c r="B15" t="n">
-        <v>75007</v>
+        <v>4778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630162</v>
+        <v>630146</v>
       </c>
       <c r="R15" t="n">
-        <v>6665729</v>
+        <v>6665497</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2073,7 +2073,7 @@
         <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,42 +2269,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>57812</v>
+        <v>58511</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2309,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2347,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,39 +2377,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B19" t="n">
-        <v>58507</v>
+        <v>57816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2414,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>126024178</v>
       </c>
       <c r="B21" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>126002219</v>
       </c>
       <c r="B22" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>126024175</v>
       </c>
       <c r="B23" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>98989</v>
+        <v>98993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002190</v>
+        <v>126002223</v>
       </c>
       <c r="B25" t="n">
-        <v>103778</v>
+        <v>95798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630188</v>
+        <v>630173</v>
       </c>
       <c r="R25" t="n">
-        <v>6665482</v>
+        <v>6665473</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,6 +3047,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002184</v>
+        <v>126002193</v>
       </c>
       <c r="B26" t="n">
-        <v>91203</v>
+        <v>95702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630041</v>
+        <v>630171</v>
       </c>
       <c r="R26" t="n">
-        <v>6665802</v>
+        <v>6665468</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3170,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B27" t="n">
-        <v>95794</v>
+        <v>91207</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3205,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R27" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3241,11 +3246,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B28" t="n">
-        <v>95698</v>
+        <v>103791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R28" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>91238</v>
+        <v>96602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R29" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B30" t="n">
-        <v>96598</v>
+        <v>91242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R30" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3566,7 +3566,7 @@
         <v>126024176</v>
       </c>
       <c r="B31" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>95698</v>
+        <v>75011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R32" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>75007</v>
+        <v>95702</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R33" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3857,7 +3857,7 @@
         <v>126024169</v>
       </c>
       <c r="B34" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>126024162</v>
       </c>
       <c r="B36" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>126002175</v>
       </c>
       <c r="B38" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4370,10 +4370,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>97450</v>
+        <v>95702</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,21 +4381,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R39" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4467,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B40" t="n">
-        <v>95698</v>
+        <v>97454</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,21 +4478,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R40" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4532,12 +4532,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4567,7 +4567,7 @@
         <v>126002213</v>
       </c>
       <c r="B41" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>126002197</v>
       </c>
       <c r="B42" t="n">
-        <v>98989</v>
+        <v>98993</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002181</v>
+        <v>126002221</v>
       </c>
       <c r="B43" t="n">
-        <v>96598</v>
+        <v>75011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630057</v>
+        <v>630152</v>
       </c>
       <c r="R43" t="n">
-        <v>6665764</v>
+        <v>6665501</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,10 +4859,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126024164</v>
+        <v>126002181</v>
       </c>
       <c r="B44" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630182</v>
+        <v>630057</v>
       </c>
       <c r="R44" t="n">
-        <v>6665719</v>
+        <v>6665764</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B45" t="n">
-        <v>75007</v>
+        <v>96602</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R45" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5153,7 +5153,7 @@
         <v>126002192</v>
       </c>
       <c r="B47" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>126002194</v>
       </c>
       <c r="B48" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>126024180</v>
       </c>
       <c r="B49" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>126024179</v>
       </c>
       <c r="B50" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B51" t="n">
-        <v>84964</v>
+        <v>80634</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R51" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,64 +5619,69 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B52" t="n">
-        <v>80630</v>
+        <v>84968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R52" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5716,21 +5721,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5740,7 +5740,7 @@
         <v>126217596</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>126217611</v>
       </c>
       <c r="B54" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>126218961</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>126217606</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>126217645</v>
       </c>
       <c r="B57" t="n">
-        <v>97016</v>
+        <v>97020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>126217612</v>
       </c>
       <c r="B58" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>126217608</v>
       </c>
       <c r="B59" t="n">
-        <v>103778</v>
+        <v>103791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>126218957</v>
       </c>
       <c r="B60" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126218955</v>
       </c>
       <c r="B61" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>126218954</v>
       </c>
       <c r="B63" t="n">
-        <v>79353</v>
+        <v>79357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>126217633</v>
       </c>
       <c r="B64" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>126217629</v>
       </c>
       <c r="B65" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>126218977</v>
       </c>
       <c r="B66" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7149,48 +7149,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126218972</v>
+        <v>126217639</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>80634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1026</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630143</v>
+        <v>630145</v>
       </c>
       <c r="R67" t="n">
-        <v>6665544</v>
+        <v>6665542</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,21 +7230,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7254,7 +7249,7 @@
         <v>126218979</v>
       </c>
       <c r="B68" t="n">
-        <v>74879</v>
+        <v>74883</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,48 +7348,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126217639</v>
+        <v>126218972</v>
       </c>
       <c r="B69" t="n">
-        <v>80630</v>
+        <v>79486</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>1026</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630145</v>
+        <v>630143</v>
       </c>
       <c r="R69" t="n">
-        <v>6665542</v>
+        <v>6665544</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7434,16 +7429,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7453,7 +7453,7 @@
         <v>126217643</v>
       </c>
       <c r="B70" t="n">
-        <v>97450</v>
+        <v>97454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>126266843</v>
       </c>
       <c r="B71" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>126266866</v>
       </c>
       <c r="B72" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>126266848</v>
       </c>
       <c r="B73" t="n">
-        <v>98989</v>
+        <v>98993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>126266859</v>
       </c>
       <c r="B74" t="n">
-        <v>97450</v>
+        <v>97454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002235</v>
+        <v>126002212</v>
       </c>
       <c r="B6" t="n">
-        <v>97020</v>
+        <v>75011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,38 +1085,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1590</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630135</v>
+        <v>630082</v>
       </c>
       <c r="R6" t="n">
-        <v>6665599</v>
+        <v>6665660</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1157,7 +1153,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1176,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B7" t="n">
-        <v>75011</v>
+        <v>97020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,34 +1182,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R7" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1255,6 +1254,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002227</v>
+        <v>126002191</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,34 +2183,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630081</v>
+        <v>630106</v>
       </c>
       <c r="R17" t="n">
-        <v>6665659</v>
+        <v>6665554</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2377,10 +2385,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002191</v>
+        <v>126002227</v>
       </c>
       <c r="B19" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,42 +2396,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630106</v>
+        <v>630081</v>
       </c>
       <c r="R19" t="n">
-        <v>6665554</v>
+        <v>6665659</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024169</v>
+        <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>57653</v>
+        <v>96602</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3865,38 +3865,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630101</v>
+        <v>630074</v>
       </c>
       <c r="R34" t="n">
-        <v>6665757</v>
+        <v>6665750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3929,11 +3925,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4057,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024162</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>96602</v>
+        <v>57653</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4068,34 +4059,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630074</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665750</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4128,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6640,32 +6640,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126218969</v>
+        <v>126218954</v>
       </c>
       <c r="B62" t="n">
-        <v>96602</v>
+        <v>79357</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6431</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630165</v>
+        <v>630052</v>
       </c>
       <c r="R62" t="n">
-        <v>6665579</v>
+        <v>6665775</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126218954</v>
+        <v>126218969</v>
       </c>
       <c r="B63" t="n">
-        <v>79357</v>
+        <v>96602</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6431</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630052</v>
+        <v>630165</v>
       </c>
       <c r="R63" t="n">
-        <v>6665775</v>
+        <v>6665579</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126217639</v>
+        <v>126218979</v>
       </c>
       <c r="B67" t="n">
-        <v>80634</v>
+        <v>74883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7160,37 +7160,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630145</v>
+        <v>630168</v>
       </c>
       <c r="R67" t="n">
-        <v>6665542</v>
+        <v>6665514</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,48 +7230,53 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126218979</v>
+        <v>126218972</v>
       </c>
       <c r="B68" t="n">
-        <v>74883</v>
+        <v>79486</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>1026</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630168</v>
+        <v>630143</v>
       </c>
       <c r="R68" t="n">
-        <v>6665514</v>
+        <v>6665544</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7330,7 +7335,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>liten ask</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7348,48 +7353,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126218972</v>
+        <v>126217639</v>
       </c>
       <c r="B69" t="n">
-        <v>79486</v>
+        <v>80634</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1026</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630143</v>
+        <v>630145</v>
       </c>
       <c r="R69" t="n">
-        <v>6665544</v>
+        <v>6665542</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7429,21 +7434,16 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>58511</v>
+        <v>96605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R4" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -947,18 +942,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -977,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B5" t="n">
-        <v>96602</v>
+        <v>58511</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R5" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1050,12 +1044,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>126002235</v>
       </c>
       <c r="B7" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>98993</v>
+        <v>98996</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002217</v>
+        <v>126002185</v>
       </c>
       <c r="B12" t="n">
-        <v>75011</v>
+        <v>91207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R12" t="n">
-        <v>6665729</v>
+        <v>6665784</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002222</v>
+        <v>126002217</v>
       </c>
       <c r="B13" t="n">
-        <v>95798</v>
+        <v>75011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,38 +1780,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630048</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665785</v>
+        <v>6665729</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1846,18 +1842,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1876,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002185</v>
+        <v>126002189</v>
       </c>
       <c r="B14" t="n">
-        <v>91207</v>
+        <v>103794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,34 +1877,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630050</v>
+        <v>630176</v>
       </c>
       <c r="R14" t="n">
-        <v>6665784</v>
+        <v>6665491</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1955,6 +1949,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1973,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002225</v>
+        <v>126002222</v>
       </c>
       <c r="B15" t="n">
-        <v>4778</v>
+        <v>95801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,34 +1979,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630146</v>
+        <v>630048</v>
       </c>
       <c r="R15" t="n">
-        <v>6665497</v>
+        <v>6665785</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2046,12 +2045,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2070,10 +2075,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002189</v>
+        <v>126002225</v>
       </c>
       <c r="B16" t="n">
-        <v>103791</v>
+        <v>4778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,38 +2086,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630176</v>
+        <v>630146</v>
       </c>
       <c r="R16" t="n">
-        <v>6665491</v>
+        <v>6665497</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2153,7 +2154,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126024178</v>
+        <v>126002196</v>
       </c>
       <c r="B21" t="n">
-        <v>75011</v>
+        <v>98996</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,37 +2590,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630163</v>
+        <v>630120</v>
       </c>
       <c r="R21" t="n">
-        <v>6665743</v>
+        <v>6665550</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2647,17 +2644,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2666,7 +2658,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2685,7 +2676,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B22" t="n">
         <v>75011</v>
@@ -2714,16 +2705,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R22" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2744,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2764,6 +2763,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
         <v>75011</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B24" t="n">
-        <v>98993</v>
+        <v>75011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B25" t="n">
-        <v>95798</v>
+        <v>91207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R25" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,11 +3047,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002193</v>
+        <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>95702</v>
+        <v>95801</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630171</v>
+        <v>630173</v>
       </c>
       <c r="R26" t="n">
-        <v>6665468</v>
+        <v>6665473</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002184</v>
+        <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>91207</v>
+        <v>95705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630041</v>
+        <v>630171</v>
       </c>
       <c r="R27" t="n">
-        <v>6665802</v>
+        <v>6665468</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3275,7 +3275,7 @@
         <v>126002190</v>
       </c>
       <c r="B28" t="n">
-        <v>103791</v>
+        <v>103794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>95702</v>
+        <v>95705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,35 +4048,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B36" t="n">
-        <v>57653</v>
+        <v>58511</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4087,10 +4088,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4117,17 +4118,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4136,6 +4137,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4154,36 +4156,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B37" t="n">
-        <v>58511</v>
+        <v>57653</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4225,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B38" t="n">
-        <v>58511</v>
+        <v>97457</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,39 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R38" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4340,18 +4335,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4373,7 +4362,7 @@
         <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>95702</v>
+        <v>95705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4467,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002224</v>
+        <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>97454</v>
+        <v>58511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,34 +4467,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>569</v>
+        <v>208250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630126</v>
+        <v>630182</v>
       </c>
       <c r="R40" t="n">
-        <v>6665560</v>
+        <v>6665478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4540,12 +4534,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002197</v>
+        <v>126002221</v>
       </c>
       <c r="B42" t="n">
-        <v>98993</v>
+        <v>75011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630142</v>
+        <v>630152</v>
       </c>
       <c r="R42" t="n">
-        <v>6665504</v>
+        <v>6665501</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B43" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R43" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4862,7 +4862,7 @@
         <v>126002181</v>
       </c>
       <c r="B44" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024164</v>
+        <v>126024182</v>
       </c>
       <c r="B45" t="n">
-        <v>96602</v>
+        <v>4778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630182</v>
+        <v>630146</v>
       </c>
       <c r="R45" t="n">
-        <v>6665719</v>
+        <v>6665537</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>4778</v>
+        <v>98996</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R46" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5150,10 +5150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126002192</v>
+        <v>126024180</v>
       </c>
       <c r="B47" t="n">
-        <v>95702</v>
+        <v>75011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5161,21 +5161,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>630144</v>
+        <v>630152</v>
       </c>
       <c r="R47" t="n">
-        <v>6665747</v>
+        <v>6665543</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002194</v>
+        <v>126024179</v>
       </c>
       <c r="B48" t="n">
-        <v>95702</v>
+        <v>75011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630166</v>
+        <v>630188</v>
       </c>
       <c r="R48" t="n">
-        <v>6665496</v>
+        <v>6665726</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024180</v>
+        <v>126002194</v>
       </c>
       <c r="B49" t="n">
-        <v>75011</v>
+        <v>95705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630152</v>
+        <v>630166</v>
       </c>
       <c r="R49" t="n">
-        <v>6665543</v>
+        <v>6665496</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,10 +5441,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126024179</v>
+        <v>126002192</v>
       </c>
       <c r="B50" t="n">
-        <v>75011</v>
+        <v>95705</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5452,21 +5452,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630188</v>
+        <v>630144</v>
       </c>
       <c r="R50" t="n">
-        <v>6665726</v>
+        <v>6665747</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B51" t="n">
-        <v>80634</v>
+        <v>84968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R51" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,69 +5619,64 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B52" t="n">
-        <v>84968</v>
+        <v>80634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R52" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5721,48 +5716,53 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126217596</v>
+        <v>126217611</v>
       </c>
       <c r="B53" t="n">
-        <v>79486</v>
+        <v>95705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1026</v>
+        <v>2818</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630144</v>
+        <v>630169</v>
       </c>
       <c r="R53" t="n">
-        <v>6665539</v>
+        <v>6665581</v>
       </c>
       <c r="S53" t="n">
         <v>12</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126217611</v>
+        <v>126217596</v>
       </c>
       <c r="B54" t="n">
-        <v>95702</v>
+        <v>79486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2818</v>
+        <v>1026</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630169</v>
+        <v>630144</v>
       </c>
       <c r="R54" t="n">
-        <v>6665581</v>
+        <v>6665539</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -5931,48 +5931,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126218961</v>
+        <v>126217606</v>
       </c>
       <c r="B55" t="n">
-        <v>79486</v>
+        <v>91242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1026</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630158</v>
+        <v>630144</v>
       </c>
       <c r="R55" t="n">
-        <v>6665746</v>
+        <v>6665539</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6004,6 +6004,11 @@
           <t>2025-06-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På stående högstubbe av gran med barken kvar.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6012,69 +6017,64 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>död ask</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126217606</v>
+        <v>126218961</v>
       </c>
       <c r="B56" t="n">
-        <v>91242</v>
+        <v>79486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1026</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630144</v>
+        <v>630158</v>
       </c>
       <c r="R56" t="n">
-        <v>6665539</v>
+        <v>6665746</v>
       </c>
       <c r="S56" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6106,11 +6106,6 @@
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På stående högstubbe av gran med barken kvar.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6119,16 +6114,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>död ask</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
         <v>126217645</v>
       </c>
       <c r="B57" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B58" t="n">
-        <v>57653</v>
+        <v>103794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R58" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B59" t="n">
-        <v>103791</v>
+        <v>57653</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R59" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6640,32 +6640,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126218954</v>
+        <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>79357</v>
+        <v>96605</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6431</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630052</v>
+        <v>630165</v>
       </c>
       <c r="R62" t="n">
-        <v>6665775</v>
+        <v>6665579</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126218969</v>
+        <v>126218954</v>
       </c>
       <c r="B63" t="n">
-        <v>96602</v>
+        <v>79357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6431</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630165</v>
+        <v>630052</v>
       </c>
       <c r="R63" t="n">
-        <v>6665579</v>
+        <v>6665775</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7453,7 +7453,7 @@
         <v>126217643</v>
       </c>
       <c r="B70" t="n">
-        <v>97454</v>
+        <v>97457</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>126266843</v>
       </c>
       <c r="B71" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>126266866</v>
       </c>
       <c r="B72" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>126266848</v>
       </c>
       <c r="B73" t="n">
-        <v>98993</v>
+        <v>98996</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>126266859</v>
       </c>
       <c r="B74" t="n">
-        <v>97454</v>
+        <v>97457</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>75011</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,34 +1085,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R6" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,6 +1157,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B7" t="n">
-        <v>97023</v>
+        <v>98996</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,38 +1187,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R7" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1254,7 +1255,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B8" t="n">
-        <v>98996</v>
+        <v>75011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R8" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002191</v>
+        <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>57816</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,42 +2183,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630106</v>
+        <v>630081</v>
       </c>
       <c r="R17" t="n">
-        <v>6665554</v>
+        <v>6665659</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2385,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002227</v>
+        <v>126002191</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2396,34 +2388,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630081</v>
+        <v>630106</v>
       </c>
       <c r="R19" t="n">
-        <v>6665659</v>
+        <v>6665554</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2482,45 +2482,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002178</v>
+        <v>126024178</v>
       </c>
       <c r="B20" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630009</v>
+        <v>630163</v>
       </c>
       <c r="R20" t="n">
-        <v>6665706</v>
+        <v>6665743</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,17 +2545,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,6 +2569,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2579,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002196</v>
+        <v>126002219</v>
       </c>
       <c r="B21" t="n">
-        <v>98996</v>
+        <v>75011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2614,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630120</v>
+        <v>630108</v>
       </c>
       <c r="R21" t="n">
-        <v>6665550</v>
+        <v>6665515</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2676,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024178</v>
+        <v>126024175</v>
       </c>
       <c r="B22" t="n">
         <v>75011</v>
@@ -2705,19 +2714,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630163</v>
+        <v>630159</v>
       </c>
       <c r="R22" t="n">
-        <v>6665743</v>
+        <v>6665738</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2752,18 +2758,12 @@
           <t>2025-06-14</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126002178</v>
       </c>
       <c r="B23" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630009</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665706</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75011</v>
+        <v>98996</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>97457</v>
+        <v>95705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B39" t="n">
-        <v>95705</v>
+        <v>97457</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R39" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4665,10 +4665,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002221</v>
+        <v>126024182</v>
       </c>
       <c r="B42" t="n">
-        <v>75011</v>
+        <v>4778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630152</v>
+        <v>630146</v>
       </c>
       <c r="R42" t="n">
-        <v>6665501</v>
+        <v>6665537</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126024164</v>
+        <v>126002197</v>
       </c>
       <c r="B43" t="n">
-        <v>96605</v>
+        <v>98996</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630182</v>
+        <v>630142</v>
       </c>
       <c r="R43" t="n">
-        <v>6665719</v>
+        <v>6665504</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002181</v>
+        <v>126002221</v>
       </c>
       <c r="B44" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630057</v>
+        <v>630152</v>
       </c>
       <c r="R44" t="n">
-        <v>6665764</v>
+        <v>6665501</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024182</v>
+        <v>126024164</v>
       </c>
       <c r="B45" t="n">
-        <v>4778</v>
+        <v>96605</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630146</v>
+        <v>630182</v>
       </c>
       <c r="R45" t="n">
-        <v>6665537</v>
+        <v>6665719</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5053,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002197</v>
+        <v>126002181</v>
       </c>
       <c r="B46" t="n">
-        <v>98996</v>
+        <v>96605</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630142</v>
+        <v>630057</v>
       </c>
       <c r="R46" t="n">
-        <v>6665504</v>
+        <v>6665764</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B51" t="n">
-        <v>84968</v>
+        <v>80634</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R51" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,64 +5619,69 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B52" t="n">
-        <v>80634</v>
+        <v>84968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R52" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5716,21 +5721,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5931,48 +5931,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126217606</v>
+        <v>126218961</v>
       </c>
       <c r="B55" t="n">
-        <v>91242</v>
+        <v>79486</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1026</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>630144</v>
+        <v>630158</v>
       </c>
       <c r="R55" t="n">
-        <v>6665539</v>
+        <v>6665746</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6004,11 +6004,6 @@
           <t>2025-06-25</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På stående högstubbe av gran med barken kvar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6017,64 +6012,69 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>död ask</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126218961</v>
+        <v>126217606</v>
       </c>
       <c r="B56" t="n">
-        <v>79486</v>
+        <v>91242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1026</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>630158</v>
+        <v>630144</v>
       </c>
       <c r="R56" t="n">
-        <v>6665746</v>
+        <v>6665539</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6106,6 +6106,11 @@
           <t>2025-06-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På stående högstubbe av gran med barken kvar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6114,21 +6119,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>död ask</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B58" t="n">
-        <v>103794</v>
+        <v>57653</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R58" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B59" t="n">
-        <v>57653</v>
+        <v>103794</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R59" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002235</v>
+        <v>126002195</v>
       </c>
       <c r="B6" t="n">
-        <v>97023</v>
+        <v>98996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,38 +1085,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1590</v>
+        <v>222302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630135</v>
+        <v>630152</v>
       </c>
       <c r="R6" t="n">
-        <v>6665599</v>
+        <v>6665487</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1157,7 +1153,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1176,10 +1171,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>98996</v>
+        <v>75011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1182,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R7" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1273,10 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002212</v>
+        <v>126002235</v>
       </c>
       <c r="B8" t="n">
-        <v>75011</v>
+        <v>97023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,34 +1279,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>1590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630082</v>
+        <v>630135</v>
       </c>
       <c r="R8" t="n">
-        <v>6665660</v>
+        <v>6665599</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1352,6 +1351,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B9" t="n">
-        <v>56602</v>
+        <v>58511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R9" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1443,12 +1448,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1467,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B10" t="n">
-        <v>58511</v>
+        <v>56602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,39 +1489,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R10" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1545,18 +1551,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002189</v>
+        <v>126002222</v>
       </c>
       <c r="B14" t="n">
-        <v>103794</v>
+        <v>95801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630176</v>
+        <v>630048</v>
       </c>
       <c r="R14" t="n">
-        <v>6665491</v>
+        <v>6665785</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1941,6 +1941,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1968,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002222</v>
+        <v>126002189</v>
       </c>
       <c r="B15" t="n">
-        <v>95801</v>
+        <v>103794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>210</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630048</v>
+        <v>630176</v>
       </c>
       <c r="R15" t="n">
-        <v>6665785</v>
+        <v>6665491</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2043,11 +2048,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,45 +2172,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>58511</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R17" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2245,12 +2250,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2269,50 +2280,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B18" t="n">
-        <v>58511</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R18" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2347,18 +2353,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126024178</v>
+        <v>126002219</v>
       </c>
       <c r="B20" t="n">
         <v>75011</v>
@@ -2511,19 +2511,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630163</v>
+        <v>630108</v>
       </c>
       <c r="R20" t="n">
-        <v>6665743</v>
+        <v>6665515</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2550,17 +2547,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2569,7 +2561,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2588,7 +2579,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002219</v>
+        <v>126024175</v>
       </c>
       <c r="B21" t="n">
         <v>75011</v>
@@ -2623,10 +2614,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630108</v>
+        <v>630159</v>
       </c>
       <c r="R21" t="n">
-        <v>6665515</v>
+        <v>6665738</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2653,12 +2644,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,32 +2676,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024175</v>
+        <v>126002178</v>
       </c>
       <c r="B22" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2711,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630159</v>
+        <v>630009</v>
       </c>
       <c r="R22" t="n">
-        <v>6665738</v>
+        <v>6665706</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2745,17 +2736,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,45 +2773,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002178</v>
+        <v>126024178</v>
       </c>
       <c r="B23" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630009</v>
+        <v>630163</v>
       </c>
       <c r="R23" t="n">
-        <v>6665706</v>
+        <v>6665743</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,17 +2836,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2861,6 +2860,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002184</v>
+        <v>126002193</v>
       </c>
       <c r="B25" t="n">
-        <v>91207</v>
+        <v>95705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630041</v>
+        <v>630171</v>
       </c>
       <c r="R25" t="n">
-        <v>6665802</v>
+        <v>6665468</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B26" t="n">
-        <v>95801</v>
+        <v>91207</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R26" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,11 +3144,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002193</v>
+        <v>126002223</v>
       </c>
       <c r="B27" t="n">
-        <v>95705</v>
+        <v>95801</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3181,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3205,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630171</v>
+        <v>630173</v>
       </c>
       <c r="R27" t="n">
-        <v>6665468</v>
+        <v>6665473</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3246,6 +3241,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3369,32 +3369,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126002180</v>
+        <v>126024176</v>
       </c>
       <c r="B29" t="n">
-        <v>96605</v>
+        <v>75011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630049</v>
+        <v>630066</v>
       </c>
       <c r="R29" t="n">
-        <v>6665789</v>
+        <v>6665750</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024166</v>
+        <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>91242</v>
+        <v>96605</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630159</v>
+        <v>630049</v>
       </c>
       <c r="R30" t="n">
-        <v>6665490</v>
+        <v>6665789</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3563,32 +3563,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126024176</v>
+        <v>126024166</v>
       </c>
       <c r="B31" t="n">
-        <v>75011</v>
+        <v>91242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630066</v>
+        <v>630159</v>
       </c>
       <c r="R31" t="n">
-        <v>6665750</v>
+        <v>6665490</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3854,45 +3854,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126024162</v>
+        <v>126002172</v>
       </c>
       <c r="B34" t="n">
-        <v>96605</v>
+        <v>58511</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630074</v>
+        <v>630047</v>
       </c>
       <c r="R34" t="n">
-        <v>6665750</v>
+        <v>6665787</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3919,12 +3924,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3933,6 +3943,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3951,10 +3962,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024163</v>
+        <v>126024169</v>
       </c>
       <c r="B35" t="n">
-        <v>96605</v>
+        <v>57653</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,34 +3973,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630065</v>
+        <v>630101</v>
       </c>
       <c r="R35" t="n">
-        <v>6665730</v>
+        <v>6665757</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4022,6 +4037,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4048,50 +4068,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126002172</v>
+        <v>126024162</v>
       </c>
       <c r="B36" t="n">
-        <v>58511</v>
+        <v>96605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630047</v>
+        <v>630074</v>
       </c>
       <c r="R36" t="n">
-        <v>6665787</v>
+        <v>6665750</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4118,17 +4133,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4137,7 +4147,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,10 +4165,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024169</v>
+        <v>126024163</v>
       </c>
       <c r="B37" t="n">
-        <v>57653</v>
+        <v>96605</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,38 +4176,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630101</v>
+        <v>630065</v>
       </c>
       <c r="R37" t="n">
-        <v>6665757</v>
+        <v>6665730</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4231,11 +4236,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B38" t="n">
-        <v>95705</v>
+        <v>58511</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,34 +4273,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R38" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4332,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4341,6 +4351,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002175</v>
+        <v>126024167</v>
       </c>
       <c r="B40" t="n">
-        <v>58511</v>
+        <v>95705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,39 +4478,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>2818</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630182</v>
+        <v>630055</v>
       </c>
       <c r="R40" t="n">
-        <v>6665478</v>
+        <v>6665749</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4526,17 +4532,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4545,7 +4546,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B42" t="n">
-        <v>4778</v>
+        <v>98996</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R42" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,10 +4762,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002197</v>
+        <v>126002221</v>
       </c>
       <c r="B43" t="n">
-        <v>98996</v>
+        <v>75011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630142</v>
+        <v>630152</v>
       </c>
       <c r="R43" t="n">
-        <v>6665504</v>
+        <v>6665501</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B44" t="n">
-        <v>75011</v>
+        <v>96605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R44" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,7 +4956,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024164</v>
+        <v>126002181</v>
       </c>
       <c r="B45" t="n">
         <v>96605</v>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630182</v>
+        <v>630057</v>
       </c>
       <c r="R45" t="n">
-        <v>6665719</v>
+        <v>6665764</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,32 +5053,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B46" t="n">
-        <v>96605</v>
+        <v>4778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R46" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126024179</v>
+        <v>126002192</v>
       </c>
       <c r="B48" t="n">
-        <v>75011</v>
+        <v>95705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630188</v>
+        <v>630144</v>
       </c>
       <c r="R48" t="n">
-        <v>6665726</v>
+        <v>6665747</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126002194</v>
+        <v>126024179</v>
       </c>
       <c r="B49" t="n">
-        <v>95705</v>
+        <v>75011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630166</v>
+        <v>630188</v>
       </c>
       <c r="R49" t="n">
-        <v>6665496</v>
+        <v>6665726</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126002192</v>
+        <v>126002194</v>
       </c>
       <c r="B50" t="n">
         <v>95705</v>
@@ -5476,10 +5476,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>630144</v>
+        <v>630166</v>
       </c>
       <c r="R50" t="n">
-        <v>6665747</v>
+        <v>6665496</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B51" t="n">
-        <v>80634</v>
+        <v>84968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R51" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,69 +5619,64 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B52" t="n">
-        <v>84968</v>
+        <v>80634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R52" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5721,16 +5716,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126218979</v>
+        <v>126217639</v>
       </c>
       <c r="B67" t="n">
-        <v>74883</v>
+        <v>80634</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7160,37 +7160,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630168</v>
+        <v>630145</v>
       </c>
       <c r="R67" t="n">
-        <v>6665514</v>
+        <v>6665542</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,21 +7230,16 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7353,10 +7348,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126217639</v>
+        <v>126218979</v>
       </c>
       <c r="B69" t="n">
-        <v>80634</v>
+        <v>74883</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7364,37 +7359,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630145</v>
+        <v>630168</v>
       </c>
       <c r="R69" t="n">
-        <v>6665542</v>
+        <v>6665514</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7434,16 +7429,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002222</v>
+        <v>126002225</v>
       </c>
       <c r="B14" t="n">
-        <v>95801</v>
+        <v>4778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,38 +1877,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>102306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630048</v>
+        <v>630146</v>
       </c>
       <c r="R14" t="n">
-        <v>6665785</v>
+        <v>6665497</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1943,18 +1939,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002225</v>
+        <v>126002222</v>
       </c>
       <c r="B16" t="n">
-        <v>4778</v>
+        <v>95801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2086,34 +2076,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630146</v>
+        <v>630048</v>
       </c>
       <c r="R16" t="n">
-        <v>6665497</v>
+        <v>6665785</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2148,12 +2142,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B20" t="n">
         <v>75011</v>
@@ -2511,16 +2511,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R20" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2547,12 +2550,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2561,6 +2569,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2676,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002178</v>
+        <v>126002196</v>
       </c>
       <c r="B22" t="n">
-        <v>96605</v>
+        <v>98996</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2711,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630009</v>
+        <v>630120</v>
       </c>
       <c r="R22" t="n">
-        <v>6665706</v>
+        <v>6665550</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2736,7 +2745,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2773,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024178</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
         <v>75011</v>
@@ -2802,19 +2811,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630163</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665743</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2841,17 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2860,7 +2861,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2879,32 +2879,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126002178</v>
       </c>
       <c r="B24" t="n">
-        <v>98996</v>
+        <v>96605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630009</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665706</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002175</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>58511</v>
+        <v>95705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,39 +4273,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208250</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630182</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665478</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4332,17 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4351,7 +4341,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4467,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>95705</v>
+        <v>58511</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,34 +4467,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R40" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4532,12 +4526,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4546,6 +4545,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,10 +4665,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126002197</v>
+        <v>126024182</v>
       </c>
       <c r="B42" t="n">
-        <v>98996</v>
+        <v>4778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4676,21 +4676,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222302</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630142</v>
+        <v>630146</v>
       </c>
       <c r="R42" t="n">
-        <v>6665504</v>
+        <v>6665537</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126024182</v>
+        <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>4778</v>
+        <v>98996</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>222302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630146</v>
+        <v>630142</v>
       </c>
       <c r="R46" t="n">
-        <v>6665537</v>
+        <v>6665504</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B51" t="n">
-        <v>84968</v>
+        <v>80634</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R51" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,64 +5619,69 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B52" t="n">
-        <v>80634</v>
+        <v>84968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R52" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5716,21 +5721,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7149,48 +7149,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126217639</v>
+        <v>126218972</v>
       </c>
       <c r="B67" t="n">
-        <v>80634</v>
+        <v>79486</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>1026</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630145</v>
+        <v>630143</v>
       </c>
       <c r="R67" t="n">
-        <v>6665542</v>
+        <v>6665544</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,48 +7230,53 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126218972</v>
+        <v>126218979</v>
       </c>
       <c r="B68" t="n">
-        <v>79486</v>
+        <v>74883</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1026</v>
+        <v>6428</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7281,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630143</v>
+        <v>630168</v>
       </c>
       <c r="R68" t="n">
-        <v>6665544</v>
+        <v>6665514</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7330,7 +7335,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>liten ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7348,10 +7353,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126218979</v>
+        <v>126217639</v>
       </c>
       <c r="B69" t="n">
-        <v>74883</v>
+        <v>80634</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7359,37 +7364,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630168</v>
+        <v>630145</v>
       </c>
       <c r="R69" t="n">
-        <v>6665514</v>
+        <v>6665542</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7429,21 +7434,16 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126002218</v>
       </c>
       <c r="B2" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126002215</v>
       </c>
       <c r="B3" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,45 +869,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B4" t="n">
-        <v>96605</v>
+        <v>58514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R4" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -942,12 +947,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,50 +977,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B5" t="n">
-        <v>58511</v>
+        <v>96614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R5" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1044,18 +1050,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>126002195</v>
       </c>
       <c r="B6" t="n">
-        <v>98996</v>
+        <v>99005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>126002235</v>
       </c>
       <c r="B8" t="n">
-        <v>97023</v>
+        <v>97032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>58511</v>
+        <v>56603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,39 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R9" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1448,18 +1443,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>56602</v>
+        <v>58514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,34 +1478,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R10" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1551,12 +1545,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1575,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126002220</v>
+        <v>126002222</v>
       </c>
       <c r="B11" t="n">
-        <v>75011</v>
+        <v>95810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1586,34 +1586,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>630162</v>
+        <v>630048</v>
       </c>
       <c r="R11" t="n">
-        <v>6665505</v>
+        <v>6665785</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1648,12 +1652,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>10 kapslar</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1672,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002185</v>
+        <v>126002225</v>
       </c>
       <c r="B12" t="n">
-        <v>91207</v>
+        <v>4778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>102306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630050</v>
+        <v>630146</v>
       </c>
       <c r="R12" t="n">
-        <v>6665784</v>
+        <v>6665497</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002217</v>
+        <v>126002220</v>
       </c>
       <c r="B13" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,7 +1817,7 @@
         <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665729</v>
+        <v>6665505</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1866,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002225</v>
+        <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>4778</v>
+        <v>91210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630146</v>
+        <v>630050</v>
       </c>
       <c r="R14" t="n">
-        <v>6665497</v>
+        <v>6665784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1963,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002189</v>
+        <v>126002217</v>
       </c>
       <c r="B15" t="n">
-        <v>103794</v>
+        <v>75014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1974,38 +1984,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>6426</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630176</v>
+        <v>630162</v>
       </c>
       <c r="R15" t="n">
-        <v>6665491</v>
+        <v>6665729</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2046,7 +2052,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2065,10 +2070,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126002222</v>
+        <v>126002189</v>
       </c>
       <c r="B16" t="n">
-        <v>95801</v>
+        <v>103803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2076,21 +2081,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>210</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2104,10 +2109,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>630048</v>
+        <v>630176</v>
       </c>
       <c r="R16" t="n">
-        <v>6665785</v>
+        <v>6665491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2140,11 +2145,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>10 kapslar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,39 +2172,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B17" t="n">
-        <v>58511</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2212,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R17" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2250,18 +2253,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>126002227</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,42 +2374,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>57816</v>
+        <v>58514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2420,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>126024178</v>
       </c>
       <c r="B20" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B21" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R21" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B22" t="n">
-        <v>98996</v>
+        <v>75014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R22" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126002178</v>
       </c>
       <c r="B23" t="n">
-        <v>75011</v>
+        <v>96614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630009</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665706</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2879,32 +2879,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002178</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>96605</v>
+        <v>99005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630009</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665706</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>95705</v>
+        <v>103803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R25" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3073,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002184</v>
+        <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>91207</v>
+        <v>95810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630041</v>
+        <v>630173</v>
       </c>
       <c r="R26" t="n">
-        <v>6665802</v>
+        <v>6665473</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002223</v>
+        <v>126002184</v>
       </c>
       <c r="B27" t="n">
-        <v>95801</v>
+        <v>91210</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3205,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630173</v>
+        <v>630041</v>
       </c>
       <c r="R27" t="n">
-        <v>6665473</v>
+        <v>6665802</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3241,11 +3246,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002190</v>
+        <v>126002193</v>
       </c>
       <c r="B28" t="n">
-        <v>103794</v>
+        <v>95714</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630188</v>
+        <v>630171</v>
       </c>
       <c r="R28" t="n">
-        <v>6665482</v>
+        <v>6665468</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3369,32 +3369,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126024176</v>
+        <v>126002180</v>
       </c>
       <c r="B29" t="n">
-        <v>75011</v>
+        <v>96614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630066</v>
+        <v>630049</v>
       </c>
       <c r="R29" t="n">
-        <v>6665750</v>
+        <v>6665789</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,32 +3466,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126002180</v>
+        <v>126024176</v>
       </c>
       <c r="B30" t="n">
-        <v>96605</v>
+        <v>75014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630049</v>
+        <v>630066</v>
       </c>
       <c r="R30" t="n">
-        <v>6665789</v>
+        <v>6665750</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3566,7 +3566,7 @@
         <v>126024166</v>
       </c>
       <c r="B31" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>95705</v>
+        <v>95714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,50 +3854,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126002172</v>
+        <v>126024162</v>
       </c>
       <c r="B34" t="n">
-        <v>58511</v>
+        <v>96614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>630047</v>
+        <v>630074</v>
       </c>
       <c r="R34" t="n">
-        <v>6665787</v>
+        <v>6665750</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3924,17 +3919,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3943,7 +3933,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126024169</v>
+        <v>126024163</v>
       </c>
       <c r="B35" t="n">
-        <v>57653</v>
+        <v>96614</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3973,38 +3962,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>630101</v>
+        <v>630065</v>
       </c>
       <c r="R35" t="n">
-        <v>6665757</v>
+        <v>6665730</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4037,11 +4022,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4068,10 +4048,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024162</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>96605</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,34 +4059,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630074</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665750</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4139,6 +4123,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4165,45 +4154,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024163</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>96605</v>
+        <v>58514</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630065</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665730</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4230,12 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B38" t="n">
-        <v>95705</v>
+        <v>97466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R38" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>97457</v>
+        <v>95714</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,21 +4370,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R39" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4459,7 +4459,7 @@
         <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>58511</v>
+        <v>58514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>126002213</v>
       </c>
       <c r="B41" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024182</v>
+        <v>126024164</v>
       </c>
       <c r="B42" t="n">
-        <v>4778</v>
+        <v>96614</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630146</v>
+        <v>630182</v>
       </c>
       <c r="R42" t="n">
-        <v>6665537</v>
+        <v>6665719</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002221</v>
+        <v>126002181</v>
       </c>
       <c r="B43" t="n">
-        <v>75011</v>
+        <v>96614</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630152</v>
+        <v>630057</v>
       </c>
       <c r="R43" t="n">
-        <v>6665501</v>
+        <v>6665764</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126024164</v>
+        <v>126002221</v>
       </c>
       <c r="B44" t="n">
-        <v>96605</v>
+        <v>75014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630182</v>
+        <v>630152</v>
       </c>
       <c r="R44" t="n">
-        <v>6665719</v>
+        <v>6665501</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126002181</v>
+        <v>126024182</v>
       </c>
       <c r="B45" t="n">
-        <v>96605</v>
+        <v>4778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630057</v>
+        <v>630146</v>
       </c>
       <c r="R45" t="n">
-        <v>6665764</v>
+        <v>6665537</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5056,7 +5056,7 @@
         <v>126002197</v>
       </c>
       <c r="B46" t="n">
-        <v>98996</v>
+        <v>99005</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>126024180</v>
       </c>
       <c r="B47" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126002192</v>
+        <v>126024179</v>
       </c>
       <c r="B48" t="n">
-        <v>95705</v>
+        <v>75014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5258,21 +5258,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>630144</v>
+        <v>630188</v>
       </c>
       <c r="R48" t="n">
-        <v>6665747</v>
+        <v>6665726</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5344,10 +5344,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126024179</v>
+        <v>126002192</v>
       </c>
       <c r="B49" t="n">
-        <v>75011</v>
+        <v>95714</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5355,21 +5355,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>630188</v>
+        <v>630144</v>
       </c>
       <c r="R49" t="n">
-        <v>6665726</v>
+        <v>6665747</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5444,7 +5444,7 @@
         <v>126002194</v>
       </c>
       <c r="B50" t="n">
-        <v>95705</v>
+        <v>95714</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5538,48 +5538,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126218973</v>
+        <v>126217641</v>
       </c>
       <c r="B51" t="n">
-        <v>80634</v>
+        <v>84971</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230185</v>
+        <v>241</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>630143</v>
+        <v>630167</v>
       </c>
       <c r="R51" t="n">
-        <v>6665544</v>
+        <v>6665576</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5619,69 +5619,64 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson, Martin Westberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126217641</v>
+        <v>126218973</v>
       </c>
       <c r="B52" t="n">
-        <v>84968</v>
+        <v>80637</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>241</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>630167</v>
+        <v>630143</v>
       </c>
       <c r="R52" t="n">
-        <v>6665576</v>
+        <v>6665544</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5721,48 +5716,53 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson, Martin Westberg</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126217611</v>
+        <v>126217596</v>
       </c>
       <c r="B53" t="n">
-        <v>95705</v>
+        <v>79489</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2818</v>
+        <v>1026</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>630169</v>
+        <v>630144</v>
       </c>
       <c r="R53" t="n">
-        <v>6665581</v>
+        <v>6665539</v>
       </c>
       <c r="S53" t="n">
         <v>12</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126217596</v>
+        <v>126217611</v>
       </c>
       <c r="B54" t="n">
-        <v>79486</v>
+        <v>95714</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1026</v>
+        <v>2818</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>630144</v>
+        <v>630169</v>
       </c>
       <c r="R54" t="n">
-        <v>6665539</v>
+        <v>6665581</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -5934,7 +5934,7 @@
         <v>126218961</v>
       </c>
       <c r="B55" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>126217606</v>
       </c>
       <c r="B56" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>126217645</v>
       </c>
       <c r="B57" t="n">
-        <v>97023</v>
+        <v>97032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B58" t="n">
-        <v>57653</v>
+        <v>103803</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R58" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B59" t="n">
-        <v>103794</v>
+        <v>57654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R59" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6439,7 +6439,7 @@
         <v>126218957</v>
       </c>
       <c r="B60" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126218955</v>
       </c>
       <c r="B61" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>126218954</v>
       </c>
       <c r="B63" t="n">
-        <v>79357</v>
+        <v>79360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>126217633</v>
       </c>
       <c r="B64" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>126217629</v>
       </c>
       <c r="B65" t="n">
-        <v>91611</v>
+        <v>91614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>126218977</v>
       </c>
       <c r="B66" t="n">
-        <v>75011</v>
+        <v>75014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>126218972</v>
       </c>
       <c r="B67" t="n">
-        <v>79486</v>
+        <v>79489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>126218979</v>
       </c>
       <c r="B68" t="n">
-        <v>74883</v>
+        <v>74886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>126217639</v>
       </c>
       <c r="B69" t="n">
-        <v>80634</v>
+        <v>80637</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>126217643</v>
       </c>
       <c r="B70" t="n">
-        <v>97457</v>
+        <v>97466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>126266843</v>
       </c>
       <c r="B71" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>126266866</v>
       </c>
       <c r="B72" t="n">
-        <v>105947</v>
+        <v>105956</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>126266848</v>
       </c>
       <c r="B73" t="n">
-        <v>98996</v>
+        <v>99005</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>126266859</v>
       </c>
       <c r="B74" t="n">
-        <v>97457</v>
+        <v>97466</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1682,10 +1682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126002225</v>
+        <v>126002220</v>
       </c>
       <c r="B12" t="n">
-        <v>4778</v>
+        <v>75014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>630146</v>
+        <v>630162</v>
       </c>
       <c r="R12" t="n">
-        <v>6665497</v>
+        <v>6665505</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002220</v>
+        <v>126002185</v>
       </c>
       <c r="B13" t="n">
-        <v>75014</v>
+        <v>91210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R13" t="n">
-        <v>6665505</v>
+        <v>6665784</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002185</v>
+        <v>126002217</v>
       </c>
       <c r="B14" t="n">
-        <v>91210</v>
+        <v>75014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R14" t="n">
-        <v>6665784</v>
+        <v>6665729</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126002217</v>
+        <v>126002225</v>
       </c>
       <c r="B15" t="n">
-        <v>75014</v>
+        <v>4778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,21 +1984,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>630162</v>
+        <v>630146</v>
       </c>
       <c r="R15" t="n">
-        <v>6665729</v>
+        <v>6665497</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2277,45 +2277,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>58514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2355,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,50 +2385,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B19" t="n">
-        <v>58514</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B32" t="n">
-        <v>75014</v>
+        <v>95714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R32" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B33" t="n">
-        <v>95714</v>
+        <v>75014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R33" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B58" t="n">
-        <v>103803</v>
+        <v>57654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R58" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B59" t="n">
-        <v>57654</v>
+        <v>103803</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R59" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7933,6 +7933,204 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126522505</v>
+      </c>
+      <c r="B75" t="n">
+        <v>75014</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>630197</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6665701</v>
+      </c>
+      <c r="S75" t="n">
+        <v>20</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126522504</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91973</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>630199</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6665751</v>
+      </c>
+      <c r="S76" t="n">
+        <v>20</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126002174</v>
+        <v>126002179</v>
       </c>
       <c r="B4" t="n">
-        <v>58514</v>
+        <v>96614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630129</v>
+        <v>630036</v>
       </c>
       <c r="R4" t="n">
-        <v>6665581</v>
+        <v>6665803</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -947,18 +942,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -977,45 +966,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126002179</v>
+        <v>126002174</v>
       </c>
       <c r="B5" t="n">
-        <v>96614</v>
+        <v>58514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>630036</v>
+        <v>630129</v>
       </c>
       <c r="R5" t="n">
-        <v>6665803</v>
+        <v>6665581</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1050,12 +1044,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1074,10 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126002195</v>
+        <v>126002235</v>
       </c>
       <c r="B6" t="n">
-        <v>99005</v>
+        <v>97032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1085,34 +1085,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222302</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>630152</v>
+        <v>630135</v>
       </c>
       <c r="R6" t="n">
-        <v>6665487</v>
+        <v>6665599</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1153,6 +1157,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1171,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002212</v>
+        <v>126002195</v>
       </c>
       <c r="B7" t="n">
-        <v>75014</v>
+        <v>99005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1182,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1206,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630082</v>
+        <v>630152</v>
       </c>
       <c r="R7" t="n">
-        <v>6665660</v>
+        <v>6665487</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1268,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002235</v>
+        <v>126002212</v>
       </c>
       <c r="B8" t="n">
-        <v>97032</v>
+        <v>75014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1279,38 +1284,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1590</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630135</v>
+        <v>630082</v>
       </c>
       <c r="R8" t="n">
-        <v>6665599</v>
+        <v>6665660</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1351,7 +1352,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126002185</v>
+        <v>126002217</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>75014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1790,21 +1790,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>630050</v>
+        <v>630162</v>
       </c>
       <c r="R13" t="n">
-        <v>6665784</v>
+        <v>6665729</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1876,10 +1876,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126002217</v>
+        <v>126002185</v>
       </c>
       <c r="B14" t="n">
-        <v>75014</v>
+        <v>91210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1887,21 +1887,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>630162</v>
+        <v>630050</v>
       </c>
       <c r="R14" t="n">
-        <v>6665729</v>
+        <v>6665784</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2277,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B18" t="n">
-        <v>58514</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R18" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2355,18 +2350,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2385,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>58514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,48 +2482,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126024178</v>
+        <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>75014</v>
+        <v>96614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630163</v>
+        <v>630009</v>
       </c>
       <c r="R20" t="n">
-        <v>6665743</v>
+        <v>6665706</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2545,22 +2542,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2569,7 +2561,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2588,7 +2579,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B21" t="n">
         <v>75014</v>
@@ -2617,16 +2608,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R21" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2653,12 +2647,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2667,6 +2666,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2685,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B22" t="n">
         <v>75014</v>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R22" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2782,32 +2782,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002178</v>
+        <v>126024175</v>
       </c>
       <c r="B23" t="n">
-        <v>96614</v>
+        <v>75014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630009</v>
+        <v>630159</v>
       </c>
       <c r="R23" t="n">
-        <v>6665706</v>
+        <v>6665738</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2842,17 +2842,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002190</v>
+        <v>126002223</v>
       </c>
       <c r="B25" t="n">
-        <v>103803</v>
+        <v>95810</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630188</v>
+        <v>630173</v>
       </c>
       <c r="R25" t="n">
-        <v>6665482</v>
+        <v>6665473</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,6 +3047,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002223</v>
+        <v>126002193</v>
       </c>
       <c r="B26" t="n">
-        <v>95810</v>
+        <v>95714</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3084,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3108,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630173</v>
+        <v>630171</v>
       </c>
       <c r="R26" t="n">
-        <v>6665473</v>
+        <v>6665468</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3144,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002193</v>
+        <v>126002190</v>
       </c>
       <c r="B28" t="n">
-        <v>95714</v>
+        <v>103803</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630171</v>
+        <v>630188</v>
       </c>
       <c r="R28" t="n">
-        <v>6665468</v>
+        <v>6665482</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126002180</v>
+        <v>126024166</v>
       </c>
       <c r="B29" t="n">
-        <v>96614</v>
+        <v>91245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>630049</v>
+        <v>630159</v>
       </c>
       <c r="R29" t="n">
-        <v>6665789</v>
+        <v>6665490</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3466,32 +3466,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126024176</v>
+        <v>126002180</v>
       </c>
       <c r="B30" t="n">
-        <v>75014</v>
+        <v>96614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>630066</v>
+        <v>630049</v>
       </c>
       <c r="R30" t="n">
-        <v>6665750</v>
+        <v>6665789</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3563,32 +3563,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126024166</v>
+        <v>126024176</v>
       </c>
       <c r="B31" t="n">
-        <v>91245</v>
+        <v>75014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>630159</v>
+        <v>630066</v>
       </c>
       <c r="R31" t="n">
-        <v>6665490</v>
+        <v>6665750</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126024168</v>
+        <v>126002214</v>
       </c>
       <c r="B32" t="n">
-        <v>95714</v>
+        <v>75014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>630198</v>
+        <v>630015</v>
       </c>
       <c r="R32" t="n">
-        <v>6665482</v>
+        <v>6665708</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3720,17 +3720,17 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126002214</v>
+        <v>126024168</v>
       </c>
       <c r="B33" t="n">
-        <v>75014</v>
+        <v>95714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>630015</v>
+        <v>630198</v>
       </c>
       <c r="R33" t="n">
-        <v>6665708</v>
+        <v>6665482</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4048,35 +4048,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>58514</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4087,10 +4088,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4117,17 +4118,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4136,6 +4137,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4154,36 +4156,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B37" t="n">
-        <v>58514</v>
+        <v>57654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4225,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>97466</v>
+        <v>95714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B39" t="n">
-        <v>95714</v>
+        <v>58514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,34 +4370,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R39" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4429,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4438,6 +4448,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B40" t="n">
-        <v>58514</v>
+        <v>97466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,39 +4478,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R40" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4534,18 +4540,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4665,32 +4665,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126024164</v>
+        <v>126002221</v>
       </c>
       <c r="B42" t="n">
-        <v>96614</v>
+        <v>75014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>630182</v>
+        <v>630152</v>
       </c>
       <c r="R42" t="n">
-        <v>6665719</v>
+        <v>6665501</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4762,32 +4762,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126002181</v>
+        <v>126002197</v>
       </c>
       <c r="B43" t="n">
-        <v>96614</v>
+        <v>99005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>630057</v>
+        <v>630142</v>
       </c>
       <c r="R43" t="n">
-        <v>6665764</v>
+        <v>6665504</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4859,32 +4859,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126002221</v>
+        <v>126024164</v>
       </c>
       <c r="B44" t="n">
-        <v>75014</v>
+        <v>96614</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>630152</v>
+        <v>630182</v>
       </c>
       <c r="R44" t="n">
-        <v>6665501</v>
+        <v>6665719</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4956,32 +4956,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126024182</v>
+        <v>126002181</v>
       </c>
       <c r="B45" t="n">
-        <v>4778</v>
+        <v>96614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>630146</v>
+        <v>630057</v>
       </c>
       <c r="R45" t="n">
-        <v>6665537</v>
+        <v>6665764</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5053,10 +5053,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126002197</v>
+        <v>126024182</v>
       </c>
       <c r="B46" t="n">
-        <v>99005</v>
+        <v>4778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5064,21 +5064,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222302</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>630142</v>
+        <v>630146</v>
       </c>
       <c r="R46" t="n">
-        <v>6665504</v>
+        <v>6665537</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5118,12 +5118,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6640,32 +6640,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126218969</v>
+        <v>126218954</v>
       </c>
       <c r="B62" t="n">
-        <v>96614</v>
+        <v>79360</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6431</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630165</v>
+        <v>630052</v>
       </c>
       <c r="R62" t="n">
-        <v>6665579</v>
+        <v>6665775</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126218954</v>
+        <v>126218969</v>
       </c>
       <c r="B63" t="n">
-        <v>79360</v>
+        <v>96614</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6431</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630052</v>
+        <v>630165</v>
       </c>
       <c r="R63" t="n">
-        <v>6665775</v>
+        <v>6665579</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7149,32 +7149,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126218972</v>
+        <v>126218979</v>
       </c>
       <c r="B67" t="n">
-        <v>79489</v>
+        <v>74886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1026</v>
+        <v>6428</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630143</v>
+        <v>630168</v>
       </c>
       <c r="R67" t="n">
-        <v>6665544</v>
+        <v>6665514</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>liten ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7251,32 +7251,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126218979</v>
+        <v>126218972</v>
       </c>
       <c r="B68" t="n">
-        <v>74886</v>
+        <v>79489</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6428</v>
+        <v>1026</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7286,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630168</v>
+        <v>630143</v>
       </c>
       <c r="R68" t="n">
-        <v>6665514</v>
+        <v>6665544</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>liten ask</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B9" t="n">
-        <v>56603</v>
+        <v>58514</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,34 +1381,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R9" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1443,12 +1448,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1467,10 +1478,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B10" t="n">
-        <v>58514</v>
+        <v>56603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,39 +1489,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R10" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1545,18 +1551,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002191</v>
+        <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,42 +2183,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630106</v>
+        <v>630081</v>
       </c>
       <c r="R17" t="n">
-        <v>6665554</v>
+        <v>6665659</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,45 +2269,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>58514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2347,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,39 +2377,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B19" t="n">
-        <v>58514</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2414,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002178</v>
+        <v>126002196</v>
       </c>
       <c r="B20" t="n">
-        <v>96614</v>
+        <v>99005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>222302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630009</v>
+        <v>630120</v>
       </c>
       <c r="R20" t="n">
-        <v>6665706</v>
+        <v>6665550</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2579,48 +2579,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126024178</v>
+        <v>126002178</v>
       </c>
       <c r="B21" t="n">
-        <v>75014</v>
+        <v>96614</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630163</v>
+        <v>630009</v>
       </c>
       <c r="R21" t="n">
-        <v>6665743</v>
+        <v>6665706</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2642,22 +2639,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2666,7 +2658,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2685,7 +2676,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126002219</v>
+        <v>126024178</v>
       </c>
       <c r="B22" t="n">
         <v>75014</v>
@@ -2714,16 +2705,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630108</v>
+        <v>630163</v>
       </c>
       <c r="R22" t="n">
-        <v>6665515</v>
+        <v>6665743</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2750,12 +2744,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2764,6 +2763,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126024175</v>
+        <v>126002219</v>
       </c>
       <c r="B23" t="n">
         <v>75014</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630159</v>
+        <v>630108</v>
       </c>
       <c r="R23" t="n">
-        <v>6665738</v>
+        <v>6665515</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126002196</v>
+        <v>126024175</v>
       </c>
       <c r="B24" t="n">
-        <v>99005</v>
+        <v>75014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630120</v>
+        <v>630159</v>
       </c>
       <c r="R24" t="n">
-        <v>6665550</v>
+        <v>6665738</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4048,36 +4048,35 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B36" t="n">
-        <v>58514</v>
+        <v>57654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4088,10 +4087,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R36" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4118,17 +4117,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4137,7 +4136,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,35 +4154,36 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B37" t="n">
-        <v>57654</v>
+        <v>58514</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4195,10 +4194,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R37" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4225,17 +4224,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4244,6 +4243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126024167</v>
+        <v>126002224</v>
       </c>
       <c r="B38" t="n">
-        <v>95714</v>
+        <v>97466</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>569</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630055</v>
+        <v>630126</v>
       </c>
       <c r="R38" t="n">
-        <v>6665749</v>
+        <v>6665560</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126002175</v>
+        <v>126024167</v>
       </c>
       <c r="B39" t="n">
-        <v>58514</v>
+        <v>95714</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,39 +4370,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208250</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630182</v>
+        <v>630055</v>
       </c>
       <c r="R39" t="n">
-        <v>6665478</v>
+        <v>6665749</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4429,17 +4424,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4448,7 +4438,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4467,10 +4456,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002224</v>
+        <v>126002175</v>
       </c>
       <c r="B40" t="n">
-        <v>97466</v>
+        <v>58514</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,34 +4467,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>569</v>
+        <v>208250</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630126</v>
+        <v>630182</v>
       </c>
       <c r="R40" t="n">
-        <v>6665560</v>
+        <v>6665478</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4540,12 +4534,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6640,32 +6640,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126218954</v>
+        <v>126218969</v>
       </c>
       <c r="B62" t="n">
-        <v>79360</v>
+        <v>96614</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6431</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>630052</v>
+        <v>630165</v>
       </c>
       <c r="R62" t="n">
-        <v>6665775</v>
+        <v>6665579</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -6742,32 +6742,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126218969</v>
+        <v>126218954</v>
       </c>
       <c r="B63" t="n">
-        <v>96614</v>
+        <v>79360</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6431</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6777,10 +6777,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>630165</v>
+        <v>630052</v>
       </c>
       <c r="R63" t="n">
-        <v>6665579</v>
+        <v>6665775</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7149,10 +7149,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126218979</v>
+        <v>126217639</v>
       </c>
       <c r="B67" t="n">
-        <v>74886</v>
+        <v>80637</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7160,37 +7160,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630168</v>
+        <v>630145</v>
       </c>
       <c r="R67" t="n">
-        <v>6665514</v>
+        <v>6665542</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,53 +7230,48 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126218972</v>
+        <v>126218979</v>
       </c>
       <c r="B68" t="n">
-        <v>79489</v>
+        <v>74886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1026</v>
+        <v>6428</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7286,10 +7281,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>630143</v>
+        <v>630168</v>
       </c>
       <c r="R68" t="n">
-        <v>6665544</v>
+        <v>6665514</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7335,7 +7330,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>liten ask</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7353,48 +7348,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126217639</v>
+        <v>126218972</v>
       </c>
       <c r="B69" t="n">
-        <v>80637</v>
+        <v>79489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>1026</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630145</v>
+        <v>630143</v>
       </c>
       <c r="R69" t="n">
-        <v>6665542</v>
+        <v>6665544</v>
       </c>
       <c r="S69" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7434,16 +7429,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126002195</v>
+        <v>126002212</v>
       </c>
       <c r="B7" t="n">
-        <v>99005</v>
+        <v>75014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222302</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>630152</v>
+        <v>630082</v>
       </c>
       <c r="R7" t="n">
-        <v>6665487</v>
+        <v>6665660</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126002212</v>
+        <v>126002195</v>
       </c>
       <c r="B8" t="n">
-        <v>75014</v>
+        <v>99005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>630082</v>
+        <v>630152</v>
       </c>
       <c r="R8" t="n">
-        <v>6665660</v>
+        <v>6665487</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002227</v>
+        <v>126002191</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,34 +2183,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630081</v>
+        <v>630106</v>
       </c>
       <c r="R17" t="n">
-        <v>6665659</v>
+        <v>6665554</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2269,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002173</v>
+        <v>126002227</v>
       </c>
       <c r="B18" t="n">
-        <v>58514</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208250</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630142</v>
+        <v>630081</v>
       </c>
       <c r="R18" t="n">
-        <v>6665664</v>
+        <v>6665659</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2347,18 +2350,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2377,42 +2374,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002191</v>
+        <v>126002173</v>
       </c>
       <c r="B19" t="n">
-        <v>57817</v>
+        <v>58514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>208250</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2420,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630106</v>
+        <v>630142</v>
       </c>
       <c r="R19" t="n">
-        <v>6665554</v>
+        <v>6665664</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2458,12 +2452,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -4048,35 +4048,36 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126024169</v>
+        <v>126002172</v>
       </c>
       <c r="B36" t="n">
-        <v>57654</v>
+        <v>58514</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>208250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4087,10 +4088,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>630101</v>
+        <v>630047</v>
       </c>
       <c r="R36" t="n">
-        <v>6665757</v>
+        <v>6665787</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4117,17 +4118,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackmärken</t>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4136,6 +4137,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4154,36 +4156,35 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126002172</v>
+        <v>126024169</v>
       </c>
       <c r="B37" t="n">
-        <v>58514</v>
+        <v>57654</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>208250</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -4194,10 +4195,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>630047</v>
+        <v>630101</v>
       </c>
       <c r="R37" t="n">
-        <v>6665787</v>
+        <v>6665757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4224,17 +4225,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
+          <t>Hackmärken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4243,7 +4244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -7149,48 +7149,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126217639</v>
+        <v>126218972</v>
       </c>
       <c r="B67" t="n">
-        <v>80637</v>
+        <v>79489</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>1026</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gogubbkärret, Upl</t>
+          <t>Liljansberg, skogsområde S om, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>630145</v>
+        <v>630143</v>
       </c>
       <c r="R67" t="n">
-        <v>6665542</v>
+        <v>6665544</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7230,16 +7230,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>liten ask</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7348,48 +7353,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126218972</v>
+        <v>126217639</v>
       </c>
       <c r="B69" t="n">
-        <v>79489</v>
+        <v>80637</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1026</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ädellav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Liljansberg, skogsområde S om, Upl</t>
+          <t>Gogubbkärret, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>630143</v>
+        <v>630145</v>
       </c>
       <c r="R69" t="n">
-        <v>6665544</v>
+        <v>6665542</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7429,21 +7434,16 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>liten ask</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Westberg, Emil V. Nilsson, Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126002171</v>
+        <v>126002186</v>
       </c>
       <c r="B9" t="n">
-        <v>58514</v>
+        <v>56603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,39 +1381,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208250</v>
+        <v>100088</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>630068</v>
+        <v>630182</v>
       </c>
       <c r="R9" t="n">
-        <v>6665679</v>
+        <v>6665493</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1448,18 +1443,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1478,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126002186</v>
+        <v>126002171</v>
       </c>
       <c r="B10" t="n">
-        <v>56603</v>
+        <v>58514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1489,34 +1478,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100088</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>630182</v>
+        <v>630068</v>
       </c>
       <c r="R10" t="n">
-        <v>6665493</v>
+        <v>6665679</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1551,12 +1545,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126002191</v>
+        <v>126002227</v>
       </c>
       <c r="B17" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2183,42 +2183,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>630106</v>
+        <v>630081</v>
       </c>
       <c r="R17" t="n">
-        <v>6665554</v>
+        <v>6665659</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2277,45 +2269,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126002227</v>
+        <v>126002173</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>58514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>208250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>630081</v>
+        <v>630142</v>
       </c>
       <c r="R18" t="n">
-        <v>6665659</v>
+        <v>6665664</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2350,12 +2347,18 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2374,39 +2377,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126002173</v>
+        <v>126002191</v>
       </c>
       <c r="B19" t="n">
-        <v>58514</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2414,10 +2420,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>630142</v>
+        <v>630106</v>
       </c>
       <c r="R19" t="n">
-        <v>6665664</v>
+        <v>6665554</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2452,18 +2458,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2482,32 +2482,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126002196</v>
+        <v>126002178</v>
       </c>
       <c r="B20" t="n">
-        <v>99005</v>
+        <v>96614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222302</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spädstarr</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carex disperma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Dewey</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>630120</v>
+        <v>630009</v>
       </c>
       <c r="R20" t="n">
-        <v>6665550</v>
+        <v>6665706</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2579,45 +2579,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126002178</v>
+        <v>126024178</v>
       </c>
       <c r="B21" t="n">
-        <v>96614</v>
+        <v>75014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>630009</v>
+        <v>630163</v>
       </c>
       <c r="R21" t="n">
-        <v>6665706</v>
+        <v>6665743</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2639,17 +2642,22 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På senvuxen gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,6 +2666,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2676,7 +2685,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126024178</v>
+        <v>126002219</v>
       </c>
       <c r="B22" t="n">
         <v>75014</v>
@@ -2705,19 +2714,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>630163</v>
+        <v>630108</v>
       </c>
       <c r="R22" t="n">
-        <v>6665743</v>
+        <v>6665515</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2744,17 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På senvuxen gran</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2763,7 +2764,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126002219</v>
+        <v>126024175</v>
       </c>
       <c r="B23" t="n">
         <v>75014</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>630108</v>
+        <v>630159</v>
       </c>
       <c r="R23" t="n">
-        <v>6665515</v>
+        <v>6665738</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2847,12 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2879,10 +2879,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126024175</v>
+        <v>126002196</v>
       </c>
       <c r="B24" t="n">
-        <v>75014</v>
+        <v>99005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>222302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spädstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carex disperma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Dewey</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>630159</v>
+        <v>630120</v>
       </c>
       <c r="R24" t="n">
-        <v>6665738</v>
+        <v>6665550</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126002223</v>
+        <v>126002190</v>
       </c>
       <c r="B25" t="n">
-        <v>95810</v>
+        <v>103803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>222412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>630173</v>
+        <v>630188</v>
       </c>
       <c r="R25" t="n">
-        <v>6665473</v>
+        <v>6665482</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,11 +3047,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126002193</v>
+        <v>126002223</v>
       </c>
       <c r="B26" t="n">
-        <v>95714</v>
+        <v>95810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3084,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>630171</v>
+        <v>630173</v>
       </c>
       <c r="R26" t="n">
-        <v>6665468</v>
+        <v>6665473</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3149,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 kapsel</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3175,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126002184</v>
+        <v>126002193</v>
       </c>
       <c r="B27" t="n">
-        <v>91210</v>
+        <v>95714</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>630041</v>
+        <v>630171</v>
       </c>
       <c r="R27" t="n">
-        <v>6665802</v>
+        <v>6665468</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126002190</v>
+        <v>126002184</v>
       </c>
       <c r="B28" t="n">
-        <v>103803</v>
+        <v>91210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,21 +3283,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>630188</v>
+        <v>630041</v>
       </c>
       <c r="R28" t="n">
-        <v>6665482</v>
+        <v>6665802</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126002224</v>
+        <v>126024167</v>
       </c>
       <c r="B38" t="n">
-        <v>97466</v>
+        <v>95714</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4273,21 +4273,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>569</v>
+        <v>2818</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>630126</v>
+        <v>630055</v>
       </c>
       <c r="R38" t="n">
-        <v>6665560</v>
+        <v>6665749</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4327,12 +4327,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4359,10 +4359,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126024167</v>
+        <v>126002175</v>
       </c>
       <c r="B39" t="n">
-        <v>95714</v>
+        <v>58514</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4370,34 +4370,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>208250</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>630055</v>
+        <v>630182</v>
       </c>
       <c r="R39" t="n">
-        <v>6665749</v>
+        <v>6665478</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4424,12 +4429,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Artbestämd bla genom att mäta grävknöl</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4438,6 +4448,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4456,10 +4467,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126002175</v>
+        <v>126002224</v>
       </c>
       <c r="B40" t="n">
-        <v>58514</v>
+        <v>97466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4467,39 +4478,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208250</v>
+        <v>569</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>630182</v>
+        <v>630126</v>
       </c>
       <c r="R40" t="n">
-        <v>6665478</v>
+        <v>6665560</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4534,18 +4540,12 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Artbestämd bla genom att mäta grävknöl</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6232,32 +6232,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126217612</v>
+        <v>126217608</v>
       </c>
       <c r="B58" t="n">
-        <v>57654</v>
+        <v>103803</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222412</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>630167</v>
+        <v>630187</v>
       </c>
       <c r="R58" t="n">
-        <v>6665616</v>
+        <v>6665511</v>
       </c>
       <c r="S58" t="n">
         <v>12</v>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Fullt utvecklade blad</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6334,32 +6334,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126217608</v>
+        <v>126217612</v>
       </c>
       <c r="B59" t="n">
-        <v>103803</v>
+        <v>57654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222412</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>630187</v>
+        <v>630167</v>
       </c>
       <c r="R59" t="n">
-        <v>6665511</v>
+        <v>6665616</v>
       </c>
       <c r="S59" t="n">
         <v>12</v>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fullt utvecklade blad</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8131,6 +8131,103 @@
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127575460</v>
+      </c>
+      <c r="B77" t="n">
+        <v>97118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>630144</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6665570</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8228,6 +8228,200 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127704823</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91102</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>630150</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6665575</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127704799</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101534</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>630175</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6665450</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97118</v>
+        <v>97120</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91102</v>
+        <v>91104</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101534</v>
+        <v>101536</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97120</v>
+        <v>97126</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91104</v>
+        <v>91110</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97126</v>
+        <v>97129</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101542</v>
+        <v>101545</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97129</v>
+        <v>97137</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91113</v>
+        <v>91121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97137</v>
+        <v>97138</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97138</v>
+        <v>97139</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8136,7 +8136,7 @@
         <v>127575460</v>
       </c>
       <c r="B77" t="n">
-        <v>97139</v>
+        <v>97140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101556</v>
+        <v>101564</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8233,7 +8233,7 @@
         <v>127704823</v>
       </c>
       <c r="B78" t="n">
-        <v>91133</v>
+        <v>91144</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>127704799</v>
       </c>
       <c r="B79" t="n">
-        <v>101564</v>
+        <v>101576</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8421,6 +8421,3974 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128593967</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>630216</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6665727</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128603908</v>
+      </c>
+      <c r="B81" t="n">
+        <v>97241</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>630132</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6665608</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128603984</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>630128</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6665547</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128603983</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>630104</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6665532</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128603982</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>630174</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6665500</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128604003</v>
+      </c>
+      <c r="B85" t="n">
+        <v>86878</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>630225</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6665721</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128604001</v>
+      </c>
+      <c r="B86" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>630109</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6665516</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128600678</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91417</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>630182</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6665691</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128603979</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>630168</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6665499</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128603988</v>
+      </c>
+      <c r="B89" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>630195</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6665720</v>
+      </c>
+      <c r="S89" t="n">
+        <v>15</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128603980</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>630114</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6665524</v>
+      </c>
+      <c r="S90" t="n">
+        <v>15</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128603985</v>
+      </c>
+      <c r="B91" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>630174</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6665585</v>
+      </c>
+      <c r="S91" t="n">
+        <v>15</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128603978</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91664</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>630165</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6665578</v>
+      </c>
+      <c r="S92" t="n">
+        <v>15</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128594301</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>630144</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6665625</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128595432</v>
+      </c>
+      <c r="B94" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>630146</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6665526</v>
+      </c>
+      <c r="S94" t="n">
+        <v>9</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128600681</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>630130</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6665565</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128603987</v>
+      </c>
+      <c r="B96" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>630190</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6665730</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128594684</v>
+      </c>
+      <c r="B97" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>630163</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6665589</v>
+      </c>
+      <c r="S97" t="n">
+        <v>6</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128600677</v>
+      </c>
+      <c r="B98" t="n">
+        <v>96823</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>53</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>630209</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6665703</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128604002</v>
+      </c>
+      <c r="B99" t="n">
+        <v>92081</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>630164</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6665682</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128603977</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91664</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>630198</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6665501</v>
+      </c>
+      <c r="S100" t="n">
+        <v>15</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128604129</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80748</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>630142</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6665540</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128603981</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>630195</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6665487</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128594920</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hocksboglupen NV, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>630062</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6665706</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128600695</v>
+      </c>
+      <c r="B104" t="n">
+        <v>100753</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>630153</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6665496</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128603930</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>630132</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6665608</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128600680</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91225</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>630153</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6665496</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128600684</v>
+      </c>
+      <c r="B107" t="n">
+        <v>90468</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>46</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rosa jodskinn</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Amylocorticium subincarnatum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Peck) Pouzar</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>630160</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6665648</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128603920</v>
+      </c>
+      <c r="B108" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>630132</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6665608</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Alec Bailey</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128603986</v>
+      </c>
+      <c r="B109" t="n">
+        <v>92387</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>630143</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6665642</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128603995</v>
+      </c>
+      <c r="B110" t="n">
+        <v>75109</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Sörsjön, söder om, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>630154</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6665564</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128596338</v>
+      </c>
+      <c r="B111" t="n">
+        <v>96019</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>210</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Liljansberg, Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>630193</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6665500</v>
+      </c>
+      <c r="S111" t="n">
+        <v>4</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128601989</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>630177</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6665502</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128601980</v>
+      </c>
+      <c r="B113" t="n">
+        <v>92074</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>483</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Rostskinn</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Crustoderma dryinum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>630132</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6665526</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128601987</v>
+      </c>
+      <c r="B114" t="n">
+        <v>86716</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>630222</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6665705</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128601974</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91664</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>630207</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6665679</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128602162</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92158</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>250072</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Erastia ochraceolateritia</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Bondartsev) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>630172</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6665588</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Tunn, liten fruktkropp med 4-5 porer/mm och rödrosa reaktion av KOH.</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128601985</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91821</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>630180</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6665493</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128601990</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Liljansberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>630136</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6665497</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Alec Bailey, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8424,7 +8424,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128593967</v>
+        <v>128603984</v>
       </c>
       <c r="B80" t="n">
         <v>92387</v>
@@ -8455,17 +8455,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>630216</v>
+        <v>630128</v>
       </c>
       <c r="R80" t="n">
-        <v>6665727</v>
+        <v>6665547</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8492,19 +8492,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8519,12 +8509,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8634,14 +8624,14 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128603984</v>
+        <v>128593967</v>
       </c>
       <c r="B82" t="n">
         <v>92387</v>
@@ -8672,17 +8662,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630128</v>
+        <v>630216</v>
       </c>
       <c r="R82" t="n">
-        <v>6665547</v>
+        <v>6665727</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8709,9 +8699,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8726,12 +8726,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8835,10 +8835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128603982</v>
+        <v>128604003</v>
       </c>
       <c r="B84" t="n">
-        <v>92387</v>
+        <v>86878</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8846,21 +8846,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8870,10 +8870,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>630174</v>
+        <v>630225</v>
       </c>
       <c r="R84" t="n">
-        <v>6665500</v>
+        <v>6665721</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -8932,10 +8932,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128604003</v>
+        <v>128603982</v>
       </c>
       <c r="B85" t="n">
-        <v>86878</v>
+        <v>92387</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8943,21 +8943,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3674</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630225</v>
+        <v>630174</v>
       </c>
       <c r="R85" t="n">
-        <v>6665721</v>
+        <v>6665500</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9417,10 +9417,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128603980</v>
+        <v>128603985</v>
       </c>
       <c r="B90" t="n">
-        <v>4773</v>
+        <v>92387</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630114</v>
+        <v>630174</v>
       </c>
       <c r="R90" t="n">
-        <v>6665524</v>
+        <v>6665585</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9514,32 +9514,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128603985</v>
+        <v>128603978</v>
       </c>
       <c r="B91" t="n">
-        <v>92387</v>
+        <v>91664</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4769</v>
+        <v>1106</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>630174</v>
+        <v>630165</v>
       </c>
       <c r="R91" t="n">
-        <v>6665585</v>
+        <v>6665578</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9611,32 +9611,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128603978</v>
+        <v>128603980</v>
       </c>
       <c r="B92" t="n">
-        <v>91664</v>
+        <v>4773</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1106</v>
+        <v>100299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630165</v>
+        <v>630114</v>
       </c>
       <c r="R92" t="n">
-        <v>6665578</v>
+        <v>6665524</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9922,10 +9922,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128600681</v>
+        <v>128603987</v>
       </c>
       <c r="B95" t="n">
-        <v>91225</v>
+        <v>92387</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9933,37 +9933,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630130</v>
+        <v>630190</v>
       </c>
       <c r="R95" t="n">
-        <v>6665565</v>
+        <v>6665730</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10007,22 +10007,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128603987</v>
+        <v>128600681</v>
       </c>
       <c r="B96" t="n">
-        <v>92387</v>
+        <v>91225</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10030,37 +10030,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630190</v>
+        <v>630130</v>
       </c>
       <c r="R96" t="n">
-        <v>6665730</v>
+        <v>6665565</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10104,69 +10104,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128594684</v>
+        <v>128600677</v>
       </c>
       <c r="B97" t="n">
-        <v>5177</v>
+        <v>96823</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>630163</v>
+        <v>630209</v>
       </c>
       <c r="R97" t="n">
-        <v>6665589</v>
+        <v>6665703</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10204,67 +10195,66 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128600677</v>
+        <v>128604002</v>
       </c>
       <c r="B98" t="n">
-        <v>96823</v>
+        <v>92081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>53</v>
+        <v>1339</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>630209</v>
+        <v>630164</v>
       </c>
       <c r="R98" t="n">
-        <v>6665703</v>
+        <v>6665682</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10308,22 +10298,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128604002</v>
+        <v>128594684</v>
       </c>
       <c r="B99" t="n">
-        <v>92081</v>
+        <v>5177</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10331,37 +10321,46 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630164</v>
+        <v>630163</v>
       </c>
       <c r="R99" t="n">
-        <v>6665682</v>
+        <v>6665589</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10399,18 +10398,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10514,10 +10514,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128604129</v>
+        <v>128603981</v>
       </c>
       <c r="B101" t="n">
-        <v>80748</v>
+        <v>92387</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10525,40 +10525,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>4769</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630142</v>
+        <v>630195</v>
       </c>
       <c r="R101" t="n">
-        <v>6665540</v>
+        <v>6665487</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10590,57 +10587,31 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128603981</v>
+        <v>128594920</v>
       </c>
       <c r="B102" t="n">
         <v>92387</v>
@@ -10671,14 +10642,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630195</v>
+        <v>630062</v>
       </c>
       <c r="R102" t="n">
-        <v>6665487</v>
+        <v>6665706</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10708,9 +10679,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10725,22 +10706,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128594920</v>
+        <v>128604129</v>
       </c>
       <c r="B103" t="n">
-        <v>92387</v>
+        <v>80748</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10748,37 +10729,40 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4769</v>
+        <v>230185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>630062</v>
+        <v>630142</v>
       </c>
       <c r="R103" t="n">
-        <v>6665706</v>
+        <v>6665540</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10805,19 +10789,14 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:24</t>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10826,18 +10805,39 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
+          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -9126,48 +9126,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128600678</v>
+        <v>128603979</v>
       </c>
       <c r="B87" t="n">
-        <v>91417</v>
+        <v>91452</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>630182</v>
+        <v>630168</v>
       </c>
       <c r="R87" t="n">
-        <v>6665691</v>
+        <v>6665499</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9211,60 +9211,60 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128603979</v>
+        <v>128600678</v>
       </c>
       <c r="B88" t="n">
-        <v>91452</v>
+        <v>91417</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>630168</v>
+        <v>630182</v>
       </c>
       <c r="R88" t="n">
-        <v>6665499</v>
+        <v>6665691</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9308,12 +9308,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128603985</v>
+        <v>128594301</v>
       </c>
       <c r="B90" t="n">
         <v>92387</v>
@@ -9448,14 +9448,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630174</v>
+        <v>630144</v>
       </c>
       <c r="R90" t="n">
-        <v>6665585</v>
+        <v>6665625</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9485,9 +9485,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9502,12 +9512,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9611,10 +9621,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128603980</v>
+        <v>128603985</v>
       </c>
       <c r="B92" t="n">
-        <v>4773</v>
+        <v>92387</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9622,21 +9632,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9646,10 +9656,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630114</v>
+        <v>630174</v>
       </c>
       <c r="R92" t="n">
-        <v>6665524</v>
+        <v>6665585</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9708,10 +9718,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128594301</v>
+        <v>128603980</v>
       </c>
       <c r="B93" t="n">
-        <v>92387</v>
+        <v>4773</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9719,34 +9729,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630144</v>
+        <v>630114</v>
       </c>
       <c r="R93" t="n">
-        <v>6665625</v>
+        <v>6665524</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9776,19 +9786,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9803,12 +9803,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 27257-2025 artfynd.xlsx
+++ b/artfynd/A 27257-2025 artfynd.xlsx
@@ -8427,7 +8427,7 @@
         <v>128603984</v>
       </c>
       <c r="B80" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8521,10 +8521,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128603908</v>
+        <v>128593967</v>
       </c>
       <c r="B81" t="n">
-        <v>97241</v>
+        <v>92393</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8532,49 +8532,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1590</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>630132</v>
+        <v>630216</v>
       </c>
       <c r="R81" t="n">
-        <v>6665608</v>
+        <v>6665727</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8601,40 +8589,49 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128593967</v>
+        <v>128603908</v>
       </c>
       <c r="B82" t="n">
-        <v>92387</v>
+        <v>97247</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8642,37 +8639,49 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4769</v>
+        <v>1590</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>630216</v>
+        <v>630132</v>
       </c>
       <c r="R82" t="n">
-        <v>6665727</v>
+        <v>6665608</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8699,39 +8708,30 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
         <v>128603983</v>
       </c>
       <c r="B83" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>128604003</v>
       </c>
       <c r="B84" t="n">
-        <v>86878</v>
+        <v>86882</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8932,10 +8932,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128603982</v>
+        <v>128604001</v>
       </c>
       <c r="B85" t="n">
-        <v>92387</v>
+        <v>5177</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8943,21 +8943,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>630174</v>
+        <v>630109</v>
       </c>
       <c r="R85" t="n">
-        <v>6665500</v>
+        <v>6665516</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9029,10 +9029,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128604001</v>
+        <v>128603982</v>
       </c>
       <c r="B86" t="n">
-        <v>5177</v>
+        <v>92393</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9040,21 +9040,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>630109</v>
+        <v>630174</v>
       </c>
       <c r="R86" t="n">
-        <v>6665516</v>
+        <v>6665500</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9129,7 +9129,7 @@
         <v>128603979</v>
       </c>
       <c r="B87" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>128600678</v>
       </c>
       <c r="B88" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>128603988</v>
       </c>
       <c r="B89" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9417,45 +9417,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128594301</v>
+        <v>128603978</v>
       </c>
       <c r="B90" t="n">
-        <v>92387</v>
+        <v>91670</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4769</v>
+        <v>1106</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>630144</v>
+        <v>630165</v>
       </c>
       <c r="R90" t="n">
-        <v>6665625</v>
+        <v>6665578</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -9485,19 +9485,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9512,44 +9502,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128603978</v>
+        <v>128603985</v>
       </c>
       <c r="B91" t="n">
-        <v>91664</v>
+        <v>92393</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1106</v>
+        <v>4769</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9559,10 +9549,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>630165</v>
+        <v>630174</v>
       </c>
       <c r="R91" t="n">
-        <v>6665578</v>
+        <v>6665585</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -9621,10 +9611,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128603985</v>
+        <v>128603980</v>
       </c>
       <c r="B92" t="n">
-        <v>92387</v>
+        <v>4773</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9632,21 +9622,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9656,10 +9646,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>630174</v>
+        <v>630114</v>
       </c>
       <c r="R92" t="n">
-        <v>6665585</v>
+        <v>6665524</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -9718,10 +9708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128603980</v>
+        <v>128594301</v>
       </c>
       <c r="B93" t="n">
-        <v>4773</v>
+        <v>92393</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9729,34 +9719,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>630114</v>
+        <v>630144</v>
       </c>
       <c r="R93" t="n">
-        <v>6665524</v>
+        <v>6665625</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -9786,9 +9776,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9803,12 +9803,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -9922,10 +9922,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128603987</v>
+        <v>128600681</v>
       </c>
       <c r="B95" t="n">
-        <v>92387</v>
+        <v>91231</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9933,37 +9933,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>630190</v>
+        <v>630130</v>
       </c>
       <c r="R95" t="n">
-        <v>6665730</v>
+        <v>6665565</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10007,22 +10007,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128600681</v>
+        <v>128603987</v>
       </c>
       <c r="B96" t="n">
-        <v>91225</v>
+        <v>92393</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10030,37 +10030,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>630130</v>
+        <v>630190</v>
       </c>
       <c r="R96" t="n">
-        <v>6665565</v>
+        <v>6665730</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10104,12 +10104,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Beke Regelin, Vilhelm Kroon, Emil V. Nilsson, Samuel Persson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -10119,7 +10119,7 @@
         <v>128600677</v>
       </c>
       <c r="B97" t="n">
-        <v>96823</v>
+        <v>96829</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10213,10 +10213,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128604002</v>
+        <v>128594684</v>
       </c>
       <c r="B98" t="n">
-        <v>92081</v>
+        <v>5177</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10224,37 +10224,46 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1339</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>630164</v>
+        <v>630163</v>
       </c>
       <c r="R98" t="n">
-        <v>6665682</v>
+        <v>6665589</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10292,28 +10301,29 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128594684</v>
+        <v>128604002</v>
       </c>
       <c r="B99" t="n">
-        <v>5177</v>
+        <v>92087</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10321,46 +10331,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100526</v>
+        <v>1339</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>630163</v>
+        <v>630164</v>
       </c>
       <c r="R99" t="n">
-        <v>6665589</v>
+        <v>6665682</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10398,19 +10399,18 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10420,7 +10420,7 @@
         <v>128603977</v>
       </c>
       <c r="B100" t="n">
-        <v>91664</v>
+        <v>91670</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10514,10 +10514,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128603981</v>
+        <v>128594920</v>
       </c>
       <c r="B101" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10545,14 +10545,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Hocksboglupen NV, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>630195</v>
+        <v>630062</v>
       </c>
       <c r="R101" t="n">
-        <v>6665487</v>
+        <v>6665706</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -10582,9 +10582,19 @@
           <t>2025-09-21</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10599,22 +10609,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128594920</v>
+        <v>128603981</v>
       </c>
       <c r="B102" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10642,14 +10652,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Hocksboglupen NV, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>630062</v>
+        <v>630195</v>
       </c>
       <c r="R102" t="n">
-        <v>6665706</v>
+        <v>6665487</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -10679,19 +10689,9 @@
           <t>2025-09-21</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10706,12 +10706,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10721,7 +10721,7 @@
         <v>128604129</v>
       </c>
       <c r="B103" t="n">
-        <v>80748</v>
+        <v>80752</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>128600695</v>
       </c>
       <c r="B104" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>128603930</v>
       </c>
       <c r="B105" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11068,7 +11068,7 @@
         <v>128600680</v>
       </c>
       <c r="B106" t="n">
-        <v>91225</v>
+        <v>91231</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>128600684</v>
       </c>
       <c r="B107" t="n">
-        <v>90468</v>
+        <v>90474</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11259,10 +11259,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128603920</v>
+        <v>128596338</v>
       </c>
       <c r="B108" t="n">
-        <v>92387</v>
+        <v>96025</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11270,48 +11270,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4769</v>
+        <v>210</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Liljansberg, Upl</t>
+          <t>Liljansberg, Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>630132</v>
+        <v>630193</v>
       </c>
       <c r="R108" t="n">
-        <v>6665608</v>
+        <v>6665500</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11349,34 +11338,18 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Elias Yngvesson, Anders Lindholm, Arvid de Jong, Beke Regelin, Emil V. Nilsson, Vilhelm Kroon, Samuel Persson, Alec Bailey</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11386,7 +11359,7 @@
         <v>128603986</v>
       </c>
       <c r="B109" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11480,10 +11453,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128603995</v>
+        <v>128603920</v>
       </c>
       <c r="B110" t="n">
-        <v>75109</v>
+        <v>92393</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11491,37 +11464,48 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6426</v>
+        <v>4769</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Sörsjön, söder om, Upl</t>
+          <t>Liljansberg, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>630154</v>
+        <v>630132</v>
       </c>
       <c r="R110" t="n">
-        <v>6665564</v>
+        <v>6665608</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11559,28 +11543,44 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alec Bailey, Samuel Persson, Vilhelm Kroon, Emil V. Nilsson, Beke Regelin, Arvid de Jong, Anders Lindholm, Elias Yngvesson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128596338</v>
+        <v>128603995</v>
       </c>
       <c r="B111" t="n">
-        <v>96019</v>
+        <v>75113</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11588,37 +11588,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Liljansberg, Liljansberg, Upl</t>
+          <t>Sörsjön, söder om, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>630193</v>
+        <v>630154</v>
       </c>
       <c r="R111" t="n">
-        <v>6665500</v>
+        <v>6665564</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11662,12 +11662,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
         <v>128601989</v>
       </c>
       <c r="B112" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>128601980</v>
       </c>
       <c r="B113" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>128601987</v>
       </c>
       <c r="B114" t="n">
-        <v>86716</v>
+        <v>86721</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>128601974</v>
       </c>
       <c r="B115" t="n">
-        <v>91664</v>
+        <v>91670</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>128602162</v>
       </c>
       <c r="B116" t="n">
-        <v>92158</v>
+        <v>92164</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>128601985</v>
       </c>
       <c r="B117" t="n">
-        <v>91821</v>
+        <v>91827</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>128601990</v>
       </c>
       <c r="B118" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
